--- a/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol_DAC_Greenfield_Patagonien\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B768F2-F080-46FD-AD96-5D2FB3D4A42E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B93056-1766-44C8-BD10-FC0C9B1A26EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="374">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1307,6 +1307,21 @@
   </si>
   <si>
     <t>kWh_th</t>
+  </si>
+  <si>
+    <t>Verkaufspreiseanalyse</t>
+  </si>
+  <si>
+    <t>Maximaler Verkaufspreis Bilanznull</t>
+  </si>
+  <si>
+    <t>calc_maxprice</t>
+  </si>
+  <si>
+    <t>Verkaufspreis Bilanznull mit Vorverkauf</t>
+  </si>
+  <si>
+    <t>calc_price</t>
   </si>
 </sst>
 </file>
@@ -1512,7 +1527,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1636,20 +1651,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1658,28 +1688,20 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3406,7 +3428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
@@ -3439,10 +3461,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="86" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3457,7 +3479,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="84"/>
+      <c r="A3" s="88"/>
       <c r="B3" s="80"/>
       <c r="C3" s="13" t="s">
         <v>108</v>
@@ -3471,7 +3493,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="84"/>
+      <c r="A4" s="88"/>
       <c r="B4" s="80"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
@@ -3485,7 +3507,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="84"/>
+      <c r="A5" s="88"/>
       <c r="B5" s="80"/>
       <c r="C5" s="13" t="s">
         <v>139</v>
@@ -3499,7 +3521,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="84"/>
+      <c r="A6" s="88"/>
       <c r="B6" s="80"/>
       <c r="C6" s="13" t="s">
         <v>142</v>
@@ -3513,7 +3535,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="84"/>
+      <c r="A7" s="88"/>
       <c r="B7" s="80"/>
       <c r="C7" s="13" t="s">
         <v>156</v>
@@ -3527,7 +3549,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="84"/>
+      <c r="A8" s="88"/>
       <c r="B8" s="80"/>
       <c r="C8" s="13" t="s">
         <v>198</v>
@@ -3541,7 +3563,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="84"/>
+      <c r="A9" s="88"/>
       <c r="B9" s="80"/>
       <c r="C9" s="13" t="s">
         <v>168</v>
@@ -3555,7 +3577,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="84"/>
+      <c r="A10" s="88"/>
       <c r="B10" s="80"/>
       <c r="C10" s="13" t="s">
         <v>190</v>
@@ -3569,13 +3591,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="84"/>
+      <c r="A11" s="88"/>
       <c r="B11" s="80"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
-      <c r="B12" s="86" t="s">
+      <c r="A12" s="88"/>
+      <c r="B12" s="83" t="s">
         <v>232</v>
       </c>
       <c r="C12" s="48" t="s">
@@ -3590,8 +3612,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="84"/>
-      <c r="B13" s="87"/>
+      <c r="A13" s="88"/>
+      <c r="B13" s="84"/>
       <c r="C13" s="45" t="s">
         <v>261</v>
       </c>
@@ -3604,8 +3626,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="84"/>
-      <c r="B14" s="87"/>
+      <c r="A14" s="88"/>
+      <c r="B14" s="84"/>
       <c r="C14" s="45" t="s">
         <v>140</v>
       </c>
@@ -3618,8 +3640,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="84"/>
-      <c r="B15" s="87"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="45" t="s">
         <v>262</v>
       </c>
@@ -3632,8 +3654,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="84"/>
-      <c r="B16" s="87"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="45" t="s">
         <v>84</v>
       </c>
@@ -3646,8 +3668,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="84"/>
-      <c r="B17" s="87"/>
+      <c r="A17" s="88"/>
+      <c r="B17" s="84"/>
       <c r="C17" s="45" t="s">
         <v>142</v>
       </c>
@@ -3660,8 +3682,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="84"/>
-      <c r="B18" s="87"/>
+      <c r="A18" s="88"/>
+      <c r="B18" s="84"/>
       <c r="C18" s="45" t="s">
         <v>156</v>
       </c>
@@ -3674,8 +3696,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="84"/>
-      <c r="B19" s="87"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="84"/>
       <c r="C19" s="45" t="s">
         <v>198</v>
       </c>
@@ -3688,8 +3710,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="84"/>
-      <c r="B20" s="87"/>
+      <c r="A20" s="88"/>
+      <c r="B20" s="84"/>
       <c r="C20" s="45" t="s">
         <v>168</v>
       </c>
@@ -3702,8 +3724,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="84"/>
-      <c r="B21" s="87"/>
+      <c r="A21" s="88"/>
+      <c r="B21" s="84"/>
       <c r="C21" s="45" t="s">
         <v>190</v>
       </c>
@@ -3716,16 +3738,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="84"/>
-      <c r="B22" s="88"/>
+      <c r="A22" s="88"/>
+      <c r="B22" s="93"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
       <c r="E22" s="53"/>
       <c r="F22" s="52"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="84"/>
-      <c r="B23" s="86" t="s">
+      <c r="A23" s="88"/>
+      <c r="B23" s="83" t="s">
         <v>297</v>
       </c>
       <c r="C23" s="45" t="s">
@@ -3740,8 +3762,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="84"/>
-      <c r="B24" s="87"/>
+      <c r="A24" s="88"/>
+      <c r="B24" s="84"/>
       <c r="C24" s="45" t="s">
         <v>108</v>
       </c>
@@ -3754,8 +3776,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="84"/>
-      <c r="B25" s="87"/>
+      <c r="A25" s="88"/>
+      <c r="B25" s="84"/>
       <c r="C25" s="45" t="s">
         <v>84</v>
       </c>
@@ -3768,8 +3790,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="84"/>
-      <c r="B26" s="87"/>
+      <c r="A26" s="88"/>
+      <c r="B26" s="84"/>
       <c r="C26" s="45" t="s">
         <v>320</v>
       </c>
@@ -3782,8 +3804,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="84"/>
-      <c r="B27" s="87"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="84"/>
       <c r="C27" s="45" t="s">
         <v>142</v>
       </c>
@@ -3796,8 +3818,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="84"/>
-      <c r="B28" s="87"/>
+      <c r="A28" s="88"/>
+      <c r="B28" s="84"/>
       <c r="C28" s="45" t="s">
         <v>156</v>
       </c>
@@ -3810,8 +3832,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="84"/>
-      <c r="B29" s="87"/>
+      <c r="A29" s="88"/>
+      <c r="B29" s="84"/>
       <c r="C29" s="45" t="s">
         <v>198</v>
       </c>
@@ -3824,8 +3846,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="84"/>
-      <c r="B30" s="87"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="84"/>
       <c r="C30" s="45" t="s">
         <v>168</v>
       </c>
@@ -3838,8 +3860,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="84"/>
-      <c r="B31" s="87"/>
+      <c r="A31" s="88"/>
+      <c r="B31" s="84"/>
       <c r="C31" s="45" t="s">
         <v>190</v>
       </c>
@@ -3852,16 +3874,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="84"/>
-      <c r="B32" s="88"/>
+      <c r="A32" s="88"/>
+      <c r="B32" s="93"/>
       <c r="C32" s="52"/>
       <c r="D32" s="52"/>
       <c r="E32" s="53"/>
       <c r="F32" s="52"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="84"/>
-      <c r="B33" s="89" t="s">
+      <c r="A33" s="88"/>
+      <c r="B33" s="94" t="s">
         <v>231</v>
       </c>
       <c r="C33" s="45" t="s">
@@ -3876,8 +3898,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="84"/>
-      <c r="B34" s="89"/>
+      <c r="A34" s="88"/>
+      <c r="B34" s="94"/>
       <c r="C34" s="45" t="s">
         <v>108</v>
       </c>
@@ -3890,8 +3912,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="84"/>
-      <c r="B35" s="89"/>
+      <c r="A35" s="88"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="45" t="s">
         <v>84</v>
       </c>
@@ -3904,8 +3926,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="84"/>
-      <c r="B36" s="89"/>
+      <c r="A36" s="88"/>
+      <c r="B36" s="94"/>
       <c r="C36" s="45" t="s">
         <v>307</v>
       </c>
@@ -3918,8 +3940,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="84"/>
-      <c r="B37" s="89"/>
+      <c r="A37" s="88"/>
+      <c r="B37" s="94"/>
       <c r="C37" s="45" t="s">
         <v>274</v>
       </c>
@@ -3932,8 +3954,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="84"/>
-      <c r="B38" s="89"/>
+      <c r="A38" s="88"/>
+      <c r="B38" s="94"/>
       <c r="C38" s="45" t="s">
         <v>142</v>
       </c>
@@ -3946,8 +3968,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="84"/>
-      <c r="B39" s="89"/>
+      <c r="A39" s="88"/>
+      <c r="B39" s="94"/>
       <c r="C39" s="45" t="s">
         <v>156</v>
       </c>
@@ -3960,8 +3982,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="84"/>
-      <c r="B40" s="89"/>
+      <c r="A40" s="88"/>
+      <c r="B40" s="94"/>
       <c r="C40" s="45" t="s">
         <v>198</v>
       </c>
@@ -3974,8 +3996,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="84"/>
-      <c r="B41" s="89"/>
+      <c r="A41" s="88"/>
+      <c r="B41" s="94"/>
       <c r="C41" s="45" t="s">
         <v>168</v>
       </c>
@@ -3988,8 +4010,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="84"/>
-      <c r="B42" s="89"/>
+      <c r="A42" s="88"/>
+      <c r="B42" s="94"/>
       <c r="C42" s="45" t="s">
         <v>190</v>
       </c>
@@ -4002,18 +4024,18 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="84"/>
-      <c r="B43" s="89"/>
+      <c r="A43" s="88"/>
+      <c r="B43" s="94"/>
       <c r="C43" s="45"/>
       <c r="D43" s="45"/>
       <c r="E43" s="50"/>
       <c r="F43" s="45"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="83" t="s">
+      <c r="A44" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="93" t="s">
+      <c r="B44" s="96" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="26" t="s">
@@ -4028,7 +4050,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="84"/>
+      <c r="A45" s="88"/>
       <c r="B45" s="82"/>
       <c r="C45" s="13" t="s">
         <v>112</v>
@@ -4042,7 +4064,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="84"/>
+      <c r="A46" s="88"/>
       <c r="B46" s="82"/>
       <c r="C46" s="13" t="s">
         <v>136</v>
@@ -4056,7 +4078,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="84"/>
+      <c r="A47" s="88"/>
       <c r="B47" s="82"/>
       <c r="C47" s="13" t="s">
         <v>137</v>
@@ -4070,7 +4092,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="84"/>
+      <c r="A48" s="88"/>
       <c r="B48" s="82"/>
       <c r="C48" s="13" t="s">
         <v>142</v>
@@ -4084,7 +4106,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="84"/>
+      <c r="A49" s="88"/>
       <c r="B49" s="82"/>
       <c r="C49" s="13" t="s">
         <v>156</v>
@@ -4098,7 +4120,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="84"/>
+      <c r="A50" s="88"/>
       <c r="B50" s="82"/>
       <c r="C50" s="13" t="s">
         <v>198</v>
@@ -4112,7 +4134,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="84"/>
+      <c r="A51" s="88"/>
       <c r="B51" s="82"/>
       <c r="C51" s="13" t="s">
         <v>168</v>
@@ -4126,7 +4148,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="84"/>
+      <c r="A52" s="88"/>
       <c r="B52" s="82"/>
       <c r="C52" s="13" t="s">
         <v>190</v>
@@ -4140,16 +4162,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="84"/>
-      <c r="B53" s="94"/>
+      <c r="A53" s="88"/>
+      <c r="B53" s="91"/>
       <c r="C53" s="37"/>
       <c r="D53" s="37"/>
       <c r="E53" s="38"/>
       <c r="F53" s="37"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="84"/>
-      <c r="B54" s="89" t="s">
+      <c r="A54" s="88"/>
+      <c r="B54" s="94" t="s">
         <v>344</v>
       </c>
       <c r="C54" s="45" t="s">
@@ -4164,8 +4186,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="84"/>
-      <c r="B55" s="89"/>
+      <c r="A55" s="88"/>
+      <c r="B55" s="94"/>
       <c r="C55" s="45" t="s">
         <v>112</v>
       </c>
@@ -4178,8 +4200,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="84"/>
-      <c r="B56" s="89"/>
+      <c r="A56" s="88"/>
+      <c r="B56" s="94"/>
       <c r="C56" s="45" t="s">
         <v>136</v>
       </c>
@@ -4192,8 +4214,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="84"/>
-      <c r="B57" s="89"/>
+      <c r="A57" s="88"/>
+      <c r="B57" s="94"/>
       <c r="C57" s="45" t="s">
         <v>137</v>
       </c>
@@ -4206,8 +4228,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="84"/>
-      <c r="B58" s="89"/>
+      <c r="A58" s="88"/>
+      <c r="B58" s="94"/>
       <c r="C58" s="45" t="s">
         <v>142</v>
       </c>
@@ -4220,8 +4242,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="84"/>
-      <c r="B59" s="89"/>
+      <c r="A59" s="88"/>
+      <c r="B59" s="94"/>
       <c r="C59" s="45" t="s">
         <v>156</v>
       </c>
@@ -4234,8 +4256,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="84"/>
-      <c r="B60" s="89"/>
+      <c r="A60" s="88"/>
+      <c r="B60" s="94"/>
       <c r="C60" s="45" t="s">
         <v>198</v>
       </c>
@@ -4248,8 +4270,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="84"/>
-      <c r="B61" s="89"/>
+      <c r="A61" s="88"/>
+      <c r="B61" s="94"/>
       <c r="C61" s="45" t="s">
         <v>168</v>
       </c>
@@ -4262,8 +4284,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="84"/>
-      <c r="B62" s="89"/>
+      <c r="A62" s="88"/>
+      <c r="B62" s="94"/>
       <c r="C62" s="45" t="s">
         <v>190</v>
       </c>
@@ -4276,16 +4298,16 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="84"/>
-      <c r="B63" s="95"/>
+      <c r="A63" s="88"/>
+      <c r="B63" s="97"/>
       <c r="C63" s="45"/>
       <c r="D63" s="45"/>
       <c r="E63" s="50"/>
       <c r="F63" s="45"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="84"/>
-      <c r="B64" s="91" t="s">
+      <c r="A64" s="88"/>
+      <c r="B64" s="90" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="35" t="s">
@@ -4300,7 +4322,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="84"/>
+      <c r="A65" s="88"/>
       <c r="B65" s="82"/>
       <c r="C65" s="13" t="s">
         <v>114</v>
@@ -4314,7 +4336,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="84"/>
+      <c r="A66" s="88"/>
       <c r="B66" s="80"/>
       <c r="C66" s="13" t="s">
         <v>112</v>
@@ -4328,7 +4350,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="84"/>
+      <c r="A67" s="88"/>
       <c r="B67" s="80"/>
       <c r="C67" s="13" t="s">
         <v>108</v>
@@ -4342,7 +4364,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="84"/>
+      <c r="A68" s="88"/>
       <c r="B68" s="80"/>
       <c r="C68" s="13" t="s">
         <v>127</v>
@@ -4356,7 +4378,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="84"/>
+      <c r="A69" s="88"/>
       <c r="B69" s="80"/>
       <c r="C69" s="13" t="s">
         <v>128</v>
@@ -4370,7 +4392,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="84"/>
+      <c r="A70" s="88"/>
       <c r="B70" s="80"/>
       <c r="C70" s="13" t="s">
         <v>142</v>
@@ -4384,7 +4406,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="84"/>
+      <c r="A71" s="88"/>
       <c r="B71" s="80"/>
       <c r="C71" s="13" t="s">
         <v>156</v>
@@ -4398,7 +4420,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="84"/>
+      <c r="A72" s="88"/>
       <c r="B72" s="80"/>
       <c r="C72" s="13" t="s">
         <v>198</v>
@@ -4412,7 +4434,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="84"/>
+      <c r="A73" s="88"/>
       <c r="B73" s="80"/>
       <c r="C73" s="13" t="s">
         <v>168</v>
@@ -4426,7 +4448,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="84"/>
+      <c r="A74" s="88"/>
       <c r="B74" s="80"/>
       <c r="C74" s="13" t="s">
         <v>190</v>
@@ -4440,18 +4462,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="90"/>
-      <c r="B75" s="92"/>
+      <c r="A75" s="89"/>
+      <c r="B75" s="95"/>
       <c r="C75" s="41"/>
       <c r="D75" s="41"/>
       <c r="E75" s="42"/>
       <c r="F75" s="41"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="83" t="s">
+      <c r="A76" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="85" t="s">
+      <c r="B76" s="86" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="26" t="s">
@@ -4466,7 +4488,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="84"/>
+      <c r="A77" s="88"/>
       <c r="B77" s="80"/>
       <c r="C77" s="13" t="s">
         <v>154</v>
@@ -4480,13 +4502,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="84"/>
+      <c r="A78" s="88"/>
       <c r="B78" s="81"/>
       <c r="E78" s="31"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="84"/>
-      <c r="B79" s="91" t="s">
+      <c r="A79" s="88"/>
+      <c r="B79" s="90" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="35" t="s">
@@ -4501,7 +4523,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="84"/>
+      <c r="A80" s="88"/>
       <c r="B80" s="82"/>
       <c r="C80" s="13" t="s">
         <v>108</v>
@@ -4515,7 +4537,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="84"/>
+      <c r="A81" s="88"/>
       <c r="B81" s="82"/>
       <c r="C81" s="13" t="s">
         <v>123</v>
@@ -4529,7 +4551,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="84"/>
+      <c r="A82" s="88"/>
       <c r="B82" s="82"/>
       <c r="C82" s="13" t="s">
         <v>142</v>
@@ -4543,7 +4565,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="84"/>
+      <c r="A83" s="88"/>
       <c r="B83" s="82"/>
       <c r="C83" s="13" t="s">
         <v>156</v>
@@ -4557,7 +4579,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="84"/>
+      <c r="A84" s="88"/>
       <c r="B84" s="82"/>
       <c r="C84" s="13" t="s">
         <v>162</v>
@@ -4571,7 +4593,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="84"/>
+      <c r="A85" s="88"/>
       <c r="B85" s="82"/>
       <c r="C85" s="13" t="s">
         <v>198</v>
@@ -4585,7 +4607,7 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="84"/>
+      <c r="A86" s="88"/>
       <c r="B86" s="82"/>
       <c r="C86" s="13" t="s">
         <v>168</v>
@@ -4599,7 +4621,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="84"/>
+      <c r="A87" s="88"/>
       <c r="B87" s="82"/>
       <c r="C87" s="13" t="s">
         <v>190</v>
@@ -4613,12 +4635,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="84"/>
-      <c r="B88" s="94"/>
+      <c r="A88" s="88"/>
+      <c r="B88" s="91"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="84"/>
-      <c r="B89" s="91" t="s">
+      <c r="A89" s="88"/>
+      <c r="B89" s="90" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="35" t="s">
@@ -4633,7 +4655,7 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="84"/>
+      <c r="A90" s="88"/>
       <c r="B90" s="82"/>
       <c r="C90" s="13" t="s">
         <v>109</v>
@@ -4647,7 +4669,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="84"/>
+      <c r="A91" s="88"/>
       <c r="B91" s="82"/>
       <c r="C91" s="13" t="s">
         <v>121</v>
@@ -4661,7 +4683,7 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="84"/>
+      <c r="A92" s="88"/>
       <c r="B92" s="82"/>
       <c r="C92" s="13" t="s">
         <v>142</v>
@@ -4675,7 +4697,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="84"/>
+      <c r="A93" s="88"/>
       <c r="B93" s="82"/>
       <c r="C93" s="13" t="s">
         <v>156</v>
@@ -4689,7 +4711,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="84"/>
+      <c r="A94" s="88"/>
       <c r="B94" s="82"/>
       <c r="C94" s="13" t="s">
         <v>162</v>
@@ -4703,7 +4725,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="84"/>
+      <c r="A95" s="88"/>
       <c r="B95" s="82"/>
       <c r="C95" s="13" t="s">
         <v>198</v>
@@ -4717,7 +4739,7 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="84"/>
+      <c r="A96" s="88"/>
       <c r="B96" s="82"/>
       <c r="C96" s="13" t="s">
         <v>168</v>
@@ -4731,7 +4753,7 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="84"/>
+      <c r="A97" s="88"/>
       <c r="B97" s="82"/>
       <c r="C97" s="13" t="s">
         <v>190</v>
@@ -4745,14 +4767,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="90"/>
-      <c r="B98" s="97"/>
+      <c r="A98" s="89"/>
+      <c r="B98" s="92"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="83" t="s">
+      <c r="A99" s="87" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="85" t="s">
+      <c r="B99" s="86" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="26" t="s">
@@ -4767,7 +4789,7 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="84"/>
+      <c r="A100" s="88"/>
       <c r="B100" s="80"/>
       <c r="C100" s="13" t="s">
         <v>230</v>
@@ -4781,7 +4803,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="84"/>
+      <c r="A101" s="88"/>
       <c r="B101" s="80"/>
       <c r="C101" s="13" t="s">
         <v>151</v>
@@ -4795,7 +4817,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="84"/>
+      <c r="A102" s="88"/>
       <c r="B102" s="81"/>
       <c r="C102" s="37"/>
       <c r="D102" s="37"/>
@@ -4803,7 +4825,7 @@
       <c r="F102" s="37"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="84"/>
+      <c r="A103" s="88"/>
       <c r="B103" s="79" t="s">
         <v>330</v>
       </c>
@@ -4819,7 +4841,7 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="84"/>
+      <c r="A104" s="88"/>
       <c r="B104" s="80"/>
       <c r="C104" s="13" t="s">
         <v>335</v>
@@ -4833,7 +4855,7 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="84"/>
+      <c r="A105" s="88"/>
       <c r="B105" s="80"/>
       <c r="C105" s="13" t="s">
         <v>336</v>
@@ -4847,12 +4869,12 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="84"/>
+      <c r="A106" s="88"/>
       <c r="B106" s="81"/>
       <c r="E106" s="33"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="84"/>
+      <c r="A107" s="88"/>
       <c r="B107" s="79" t="s">
         <v>79</v>
       </c>
@@ -4868,7 +4890,7 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="84"/>
+      <c r="A108" s="88"/>
       <c r="B108" s="80"/>
       <c r="C108" s="13" t="s">
         <v>152</v>
@@ -4882,7 +4904,7 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="84"/>
+      <c r="A109" s="88"/>
       <c r="B109" s="81"/>
       <c r="C109" s="37"/>
       <c r="D109" s="37"/>
@@ -4890,8 +4912,8 @@
       <c r="F109" s="37"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="84"/>
-      <c r="B110" s="86" t="s">
+      <c r="A110" s="88"/>
+      <c r="B110" s="83" t="s">
         <v>276</v>
       </c>
       <c r="C110" s="45" t="s">
@@ -4906,8 +4928,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="84"/>
-      <c r="B111" s="87"/>
+      <c r="A111" s="88"/>
+      <c r="B111" s="84"/>
       <c r="C111" s="45" t="s">
         <v>277</v>
       </c>
@@ -4920,18 +4942,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="90"/>
-      <c r="B112" s="96"/>
+      <c r="A112" s="89"/>
+      <c r="B112" s="85"/>
       <c r="C112" s="54"/>
       <c r="D112" s="54"/>
       <c r="E112" s="55"/>
       <c r="F112" s="54"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="83" t="s">
+      <c r="A113" s="87" t="s">
         <v>164</v>
       </c>
-      <c r="B113" s="85" t="s">
+      <c r="B113" s="86" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="26" t="s">
@@ -4946,7 +4968,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="84"/>
+      <c r="A114" s="100"/>
       <c r="B114" s="80"/>
       <c r="C114" s="13" t="s">
         <v>175</v>
@@ -4959,7 +4981,7 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="84"/>
+      <c r="A115" s="100"/>
       <c r="B115" s="81"/>
       <c r="C115" s="37"/>
       <c r="D115" s="37"/>
@@ -4967,7 +4989,7 @@
       <c r="F115" s="37"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="84"/>
+      <c r="A116" s="100"/>
       <c r="B116" s="79" t="s">
         <v>184</v>
       </c>
@@ -4982,7 +5004,7 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="84"/>
+      <c r="A117" s="100"/>
       <c r="B117" s="80"/>
       <c r="C117" s="13" t="s">
         <v>182</v>
@@ -4995,7 +5017,7 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="84"/>
+      <c r="A118" s="100"/>
       <c r="B118" s="80"/>
       <c r="C118" s="13" t="s">
         <v>178</v>
@@ -5008,7 +5030,7 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="84"/>
+      <c r="A119" s="100"/>
       <c r="B119" s="80"/>
       <c r="C119" s="13" t="s">
         <v>180</v>
@@ -5021,7 +5043,7 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="84"/>
+      <c r="A120" s="100"/>
       <c r="B120" s="80"/>
       <c r="C120" s="13" t="s">
         <v>183</v>
@@ -5034,7 +5056,7 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="84"/>
+      <c r="A121" s="100"/>
       <c r="B121" s="80"/>
       <c r="C121" s="13" t="s">
         <v>193</v>
@@ -5047,11 +5069,11 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="84"/>
+      <c r="A122" s="100"/>
       <c r="B122" s="80"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="84"/>
+      <c r="A123" s="100"/>
       <c r="B123" s="79" t="s">
         <v>208</v>
       </c>
@@ -5067,7 +5089,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="84"/>
+      <c r="A124" s="100"/>
       <c r="B124" s="80"/>
       <c r="C124" s="13" t="s">
         <v>206</v>
@@ -5080,7 +5102,7 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="84"/>
+      <c r="A125" s="100"/>
       <c r="B125" s="80"/>
       <c r="C125" s="13" t="s">
         <v>217</v>
@@ -5093,7 +5115,7 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="84"/>
+      <c r="A126" s="100"/>
       <c r="B126" s="80"/>
       <c r="C126" s="13" t="s">
         <v>207</v>
@@ -5106,7 +5128,7 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="84"/>
+      <c r="A127" s="100"/>
       <c r="B127" s="80"/>
       <c r="C127" s="13" t="s">
         <v>339</v>
@@ -5119,7 +5141,7 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="84"/>
+      <c r="A128" s="100"/>
       <c r="B128" s="80"/>
       <c r="C128" s="45" t="s">
         <v>363</v>
@@ -5133,7 +5155,7 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="84"/>
+      <c r="A129" s="100"/>
       <c r="B129" s="80"/>
       <c r="C129" s="45" t="s">
         <v>365</v>
@@ -5147,7 +5169,7 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="84"/>
+      <c r="A130" s="100"/>
       <c r="B130" s="80"/>
       <c r="C130" s="13" t="s">
         <v>219</v>
@@ -5160,7 +5182,7 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="84"/>
+      <c r="A131" s="100"/>
       <c r="B131" s="80"/>
       <c r="C131" s="13" t="s">
         <v>223</v>
@@ -5173,7 +5195,7 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="84"/>
+      <c r="A132" s="100"/>
       <c r="B132" s="80"/>
       <c r="C132" s="13" t="s">
         <v>204</v>
@@ -5186,7 +5208,7 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="84"/>
+      <c r="A133" s="100"/>
       <c r="B133" s="80"/>
       <c r="C133" s="45" t="s">
         <v>280</v>
@@ -5200,7 +5222,7 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="84"/>
+      <c r="A134" s="100"/>
       <c r="B134" s="80"/>
       <c r="C134" s="45" t="s">
         <v>283</v>
@@ -5214,7 +5236,7 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="84"/>
+      <c r="A135" s="100"/>
       <c r="B135" s="80"/>
       <c r="C135" s="45"/>
       <c r="D135" s="45"/>
@@ -5222,7 +5244,7 @@
       <c r="F135" s="45"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="84"/>
+      <c r="A136" s="100"/>
       <c r="B136" s="79" t="s">
         <v>224</v>
       </c>
@@ -5238,8 +5260,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="84"/>
-      <c r="B137" s="80"/>
+      <c r="A137" s="100"/>
+      <c r="B137" s="98"/>
       <c r="C137" s="13" t="s">
         <v>341</v>
       </c>
@@ -5251,8 +5273,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="84"/>
-      <c r="B138" s="80"/>
+      <c r="A138" s="100"/>
+      <c r="B138" s="98"/>
       <c r="C138" s="13" t="s">
         <v>227</v>
       </c>
@@ -5264,8 +5286,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="84"/>
-      <c r="B139" s="80"/>
+      <c r="A139" s="100"/>
+      <c r="B139" s="98"/>
       <c r="C139" s="45" t="s">
         <v>284</v>
       </c>
@@ -5278,8 +5300,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="84"/>
-      <c r="B140" s="80"/>
+      <c r="A140" s="100"/>
+      <c r="B140" s="98"/>
       <c r="C140" s="45" t="s">
         <v>286</v>
       </c>
@@ -5291,13 +5313,56 @@
         <v>215</v>
       </c>
     </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="100"/>
+      <c r="B141" s="98"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="100"/>
+      <c r="B142" s="79" t="s">
+        <v>369</v>
+      </c>
+      <c r="C142" s="35" t="s">
+        <v>370</v>
+      </c>
+      <c r="D142" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="E142" s="35"/>
+      <c r="F142" s="35" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="100"/>
+      <c r="B143" s="98"/>
+      <c r="C143" s="99" t="s">
+        <v>372</v>
+      </c>
+      <c r="D143" s="99" t="s">
+        <v>373</v>
+      </c>
+      <c r="E143" s="99"/>
+      <c r="F143" s="99" t="s">
+        <v>299</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="A113:A143"/>
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A44:A75"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="B54:B63"/>
     <mergeCell ref="B110:B112"/>
     <mergeCell ref="B76:B78"/>
     <mergeCell ref="B116:B122"/>
-    <mergeCell ref="B136:B140"/>
-    <mergeCell ref="A113:A140"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
     <mergeCell ref="A76:A98"/>
@@ -5307,15 +5372,7 @@
     <mergeCell ref="B107:B109"/>
     <mergeCell ref="B99:B102"/>
     <mergeCell ref="B103:B106"/>
-    <mergeCell ref="A2:A43"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
+    <mergeCell ref="B136:B141"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B93056-1766-44C8-BD10-FC0C9B1A26EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E45B32E-1EE8-4998-8E88-69AC3D5D54E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="375">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1322,6 +1322,9 @@
   </si>
   <si>
     <t>calc_price</t>
+  </si>
+  <si>
+    <t>kWh_th/a</t>
   </si>
 </sst>
 </file>
@@ -1527,7 +1530,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1606,6 +1609,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1651,35 +1655,26 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1688,20 +1683,25 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2232,10 +2232,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="79" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2252,8 +2252,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="69"/>
-      <c r="B3" s="76"/>
+      <c r="A3" s="70"/>
+      <c r="B3" s="77"/>
       <c r="C3" t="s">
         <v>84</v>
       </c>
@@ -2268,8 +2268,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="69"/>
-      <c r="B4" s="76"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="77"/>
       <c r="C4" t="s">
         <v>10</v>
       </c>
@@ -2284,8 +2284,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="69"/>
-      <c r="B5" s="76"/>
+      <c r="A5" s="70"/>
+      <c r="B5" s="77"/>
       <c r="C5" t="s">
         <v>11</v>
       </c>
@@ -2300,8 +2300,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="69"/>
-      <c r="B6" s="76"/>
+      <c r="A6" s="70"/>
+      <c r="B6" s="77"/>
       <c r="C6" t="s">
         <v>13</v>
       </c>
@@ -2316,8 +2316,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="69"/>
-      <c r="B7" s="76"/>
+      <c r="A7" s="70"/>
+      <c r="B7" s="77"/>
       <c r="C7" t="s">
         <v>15</v>
       </c>
@@ -2332,8 +2332,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="69"/>
-      <c r="B8" s="79" t="s">
+      <c r="A8" s="70"/>
+      <c r="B8" s="80" t="s">
         <v>232</v>
       </c>
       <c r="C8" s="35" t="s">
@@ -2350,8 +2350,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="69"/>
-      <c r="B9" s="80"/>
+      <c r="A9" s="70"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="45" t="s">
         <v>85</v>
       </c>
@@ -2366,8 +2366,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="69"/>
-      <c r="B10" s="80"/>
+      <c r="A10" s="70"/>
+      <c r="B10" s="81"/>
       <c r="C10" s="13" t="s">
         <v>10</v>
       </c>
@@ -2382,8 +2382,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="69"/>
-      <c r="B11" s="80"/>
+      <c r="A11" s="70"/>
+      <c r="B11" s="81"/>
       <c r="C11" s="13" t="s">
         <v>11</v>
       </c>
@@ -2398,8 +2398,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="69"/>
-      <c r="B12" s="80"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="81"/>
       <c r="C12" s="13" t="s">
         <v>86</v>
       </c>
@@ -2414,8 +2414,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="69"/>
-      <c r="B13" s="80"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="45" t="s">
         <v>252</v>
       </c>
@@ -2430,8 +2430,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="69"/>
-      <c r="B14" s="80"/>
+      <c r="A14" s="70"/>
+      <c r="B14" s="81"/>
       <c r="C14" s="13" t="s">
         <v>13</v>
       </c>
@@ -2446,8 +2446,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="69"/>
-      <c r="B15" s="81"/>
+      <c r="A15" s="70"/>
+      <c r="B15" s="82"/>
       <c r="C15" s="37" t="s">
         <v>15</v>
       </c>
@@ -2462,8 +2462,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="79" t="s">
+      <c r="A16" s="70"/>
+      <c r="B16" s="80" t="s">
         <v>297</v>
       </c>
       <c r="C16" s="35" t="s">
@@ -2480,8 +2480,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="69"/>
-      <c r="B17" s="80"/>
+      <c r="A17" s="70"/>
+      <c r="B17" s="81"/>
       <c r="C17" s="13" t="s">
         <v>84</v>
       </c>
@@ -2496,8 +2496,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="69"/>
-      <c r="B18" s="80"/>
+      <c r="A18" s="70"/>
+      <c r="B18" s="81"/>
       <c r="C18" s="13" t="s">
         <v>10</v>
       </c>
@@ -2512,8 +2512,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="69"/>
-      <c r="B19" s="80"/>
+      <c r="A19" s="70"/>
+      <c r="B19" s="81"/>
       <c r="C19" s="13" t="s">
         <v>11</v>
       </c>
@@ -2528,8 +2528,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="69"/>
-      <c r="B20" s="80"/>
+      <c r="A20" s="70"/>
+      <c r="B20" s="81"/>
       <c r="C20" s="13" t="s">
         <v>13</v>
       </c>
@@ -2544,8 +2544,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="69"/>
-      <c r="B21" s="81"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="82"/>
       <c r="C21" s="37" t="s">
         <v>15</v>
       </c>
@@ -2560,8 +2560,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="69"/>
-      <c r="B22" s="82" t="s">
+      <c r="A22" s="70"/>
+      <c r="B22" s="83" t="s">
         <v>231</v>
       </c>
       <c r="C22" s="45" t="s">
@@ -2578,8 +2578,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="69"/>
-      <c r="B23" s="82"/>
+      <c r="A23" s="70"/>
+      <c r="B23" s="83"/>
       <c r="C23" s="45" t="s">
         <v>307</v>
       </c>
@@ -2594,8 +2594,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="69"/>
-      <c r="B24" s="82"/>
+      <c r="A24" s="70"/>
+      <c r="B24" s="83"/>
       <c r="C24" s="45" t="s">
         <v>10</v>
       </c>
@@ -2610,8 +2610,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="69"/>
-      <c r="B25" s="82"/>
+      <c r="A25" s="70"/>
+      <c r="B25" s="83"/>
       <c r="C25" s="45" t="s">
         <v>11</v>
       </c>
@@ -2626,8 +2626,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="69"/>
-      <c r="B26" s="82"/>
+      <c r="A26" s="70"/>
+      <c r="B26" s="83"/>
       <c r="C26" s="45" t="s">
         <v>13</v>
       </c>
@@ -2642,8 +2642,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="69"/>
-      <c r="B27" s="82"/>
+      <c r="A27" s="70"/>
+      <c r="B27" s="83"/>
       <c r="C27" s="45" t="s">
         <v>15</v>
       </c>
@@ -2658,10 +2658,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="68" t="s">
+      <c r="A28" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="71" t="s">
+      <c r="B28" s="72" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -2678,8 +2678,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="69"/>
-      <c r="B29" s="72"/>
+      <c r="A29" s="70"/>
+      <c r="B29" s="73"/>
       <c r="C29" t="s">
         <v>11</v>
       </c>
@@ -2694,8 +2694,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="69"/>
-      <c r="B30" s="72"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="73"/>
       <c r="C30" t="s">
         <v>13</v>
       </c>
@@ -2710,8 +2710,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="69"/>
-      <c r="B31" s="72"/>
+      <c r="A31" s="70"/>
+      <c r="B31" s="73"/>
       <c r="C31" t="s">
         <v>20</v>
       </c>
@@ -2726,8 +2726,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="69"/>
-      <c r="B32" s="72"/>
+      <c r="A32" s="70"/>
+      <c r="B32" s="73"/>
       <c r="C32" t="s">
         <v>35</v>
       </c>
@@ -2742,8 +2742,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="69"/>
-      <c r="B33" s="72"/>
+      <c r="A33" s="70"/>
+      <c r="B33" s="73"/>
       <c r="C33" t="s">
         <v>36</v>
       </c>
@@ -2758,8 +2758,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="69"/>
-      <c r="B34" s="72"/>
+      <c r="A34" s="70"/>
+      <c r="B34" s="73"/>
       <c r="C34" t="s">
         <v>15</v>
       </c>
@@ -2774,8 +2774,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="69"/>
-      <c r="B35" s="73"/>
+      <c r="A35" s="70"/>
+      <c r="B35" s="74"/>
       <c r="C35" s="5" t="s">
         <v>88</v>
       </c>
@@ -2790,8 +2790,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="69"/>
-      <c r="B36" s="74" t="s">
+      <c r="A36" s="70"/>
+      <c r="B36" s="75" t="s">
         <v>344</v>
       </c>
       <c r="C36" s="26" t="s">
@@ -2808,8 +2808,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="69"/>
-      <c r="B37" s="72"/>
+      <c r="A37" s="70"/>
+      <c r="B37" s="73"/>
       <c r="C37" s="13" t="s">
         <v>11</v>
       </c>
@@ -2824,8 +2824,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="69"/>
-      <c r="B38" s="72"/>
+      <c r="A38" s="70"/>
+      <c r="B38" s="73"/>
       <c r="C38" s="13" t="s">
         <v>13</v>
       </c>
@@ -2840,8 +2840,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="69"/>
-      <c r="B39" s="72"/>
+      <c r="A39" s="70"/>
+      <c r="B39" s="73"/>
       <c r="C39" s="13" t="s">
         <v>20</v>
       </c>
@@ -2856,8 +2856,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="69"/>
-      <c r="B40" s="72"/>
+      <c r="A40" s="70"/>
+      <c r="B40" s="73"/>
       <c r="C40" s="13" t="s">
         <v>35</v>
       </c>
@@ -2872,8 +2872,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="69"/>
-      <c r="B41" s="72"/>
+      <c r="A41" s="70"/>
+      <c r="B41" s="73"/>
       <c r="C41" s="13" t="s">
         <v>36</v>
       </c>
@@ -2888,8 +2888,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="69"/>
-      <c r="B42" s="72"/>
+      <c r="A42" s="70"/>
+      <c r="B42" s="73"/>
       <c r="C42" s="13" t="s">
         <v>15</v>
       </c>
@@ -2904,8 +2904,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="69"/>
-      <c r="B43" s="72"/>
+      <c r="A43" s="70"/>
+      <c r="B43" s="73"/>
       <c r="C43" s="37" t="s">
         <v>88</v>
       </c>
@@ -2920,8 +2920,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="69"/>
-      <c r="B44" s="74" t="s">
+      <c r="A44" s="70"/>
+      <c r="B44" s="75" t="s">
         <v>203</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -2938,8 +2938,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="69"/>
-      <c r="B45" s="76"/>
+      <c r="A45" s="70"/>
+      <c r="B45" s="77"/>
       <c r="C45" t="s">
         <v>21</v>
       </c>
@@ -2955,8 +2955,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="69"/>
-      <c r="B46" s="76"/>
+      <c r="A46" s="70"/>
+      <c r="B46" s="77"/>
       <c r="C46" t="s">
         <v>16</v>
       </c>
@@ -2971,8 +2971,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="69"/>
-      <c r="B47" s="76"/>
+      <c r="A47" s="70"/>
+      <c r="B47" s="77"/>
       <c r="C47" t="s">
         <v>17</v>
       </c>
@@ -2987,8 +2987,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="69"/>
-      <c r="B48" s="76"/>
+      <c r="A48" s="70"/>
+      <c r="B48" s="77"/>
       <c r="C48" t="s">
         <v>35</v>
       </c>
@@ -3003,8 +3003,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="69"/>
-      <c r="B49" s="76"/>
+      <c r="A49" s="70"/>
+      <c r="B49" s="77"/>
       <c r="C49" t="s">
         <v>36</v>
       </c>
@@ -3019,8 +3019,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="69"/>
-      <c r="B50" s="76"/>
+      <c r="A50" s="70"/>
+      <c r="B50" s="77"/>
       <c r="C50" t="s">
         <v>89</v>
       </c>
@@ -3035,8 +3035,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="69"/>
-      <c r="B51" s="76"/>
+      <c r="A51" s="70"/>
+      <c r="B51" s="77"/>
       <c r="C51" t="s">
         <v>88</v>
       </c>
@@ -3051,8 +3051,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="69"/>
-      <c r="B52" s="76"/>
+      <c r="A52" s="70"/>
+      <c r="B52" s="77"/>
       <c r="C52" t="s">
         <v>13</v>
       </c>
@@ -3067,8 +3067,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="70"/>
-      <c r="B53" s="77"/>
+      <c r="A53" s="71"/>
+      <c r="B53" s="78"/>
       <c r="C53" s="15" t="s">
         <v>15</v>
       </c>
@@ -3083,7 +3083,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="68" t="s">
+      <c r="A54" s="69" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="11" t="s">
@@ -3103,8 +3103,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="69"/>
-      <c r="B55" s="74" t="s">
+      <c r="A55" s="70"/>
+      <c r="B55" s="75" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="4" t="s">
@@ -3121,8 +3121,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="69"/>
-      <c r="B56" s="72"/>
+      <c r="A56" s="70"/>
+      <c r="B56" s="73"/>
       <c r="C56" t="s">
         <v>10</v>
       </c>
@@ -3137,8 +3137,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="69"/>
-      <c r="B57" s="72"/>
+      <c r="A57" s="70"/>
+      <c r="B57" s="73"/>
       <c r="C57" t="s">
         <v>17</v>
       </c>
@@ -3153,8 +3153,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="69"/>
-      <c r="B58" s="72"/>
+      <c r="A58" s="70"/>
+      <c r="B58" s="73"/>
       <c r="C58" t="s">
         <v>18</v>
       </c>
@@ -3169,8 +3169,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="69"/>
-      <c r="B59" s="72"/>
+      <c r="A59" s="70"/>
+      <c r="B59" s="73"/>
       <c r="C59" t="s">
         <v>13</v>
       </c>
@@ -3185,8 +3185,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="69"/>
-      <c r="B60" s="72"/>
+      <c r="A60" s="70"/>
+      <c r="B60" s="73"/>
       <c r="C60" t="s">
         <v>68</v>
       </c>
@@ -3201,8 +3201,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="69"/>
-      <c r="B61" s="73"/>
+      <c r="A61" s="70"/>
+      <c r="B61" s="74"/>
       <c r="C61" s="5" t="s">
         <v>15</v>
       </c>
@@ -3217,8 +3217,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="69"/>
-      <c r="B62" s="74" t="s">
+      <c r="A62" s="70"/>
+      <c r="B62" s="75" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -3235,8 +3235,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="69"/>
-      <c r="B63" s="72"/>
+      <c r="A63" s="70"/>
+      <c r="B63" s="73"/>
       <c r="C63" t="s">
         <v>10</v>
       </c>
@@ -3251,8 +3251,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="69"/>
-      <c r="B64" s="72"/>
+      <c r="A64" s="70"/>
+      <c r="B64" s="73"/>
       <c r="C64" t="s">
         <v>17</v>
       </c>
@@ -3267,8 +3267,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="69"/>
-      <c r="B65" s="72"/>
+      <c r="A65" s="70"/>
+      <c r="B65" s="73"/>
       <c r="C65" t="s">
         <v>18</v>
       </c>
@@ -3283,8 +3283,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="69"/>
-      <c r="B66" s="72"/>
+      <c r="A66" s="70"/>
+      <c r="B66" s="73"/>
       <c r="C66" t="s">
         <v>13</v>
       </c>
@@ -3299,8 +3299,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="69"/>
-      <c r="B67" s="72"/>
+      <c r="A67" s="70"/>
+      <c r="B67" s="73"/>
       <c r="C67" t="s">
         <v>68</v>
       </c>
@@ -3315,8 +3315,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="70"/>
-      <c r="B68" s="75"/>
+      <c r="A68" s="71"/>
+      <c r="B68" s="76"/>
       <c r="C68" s="15" t="s">
         <v>15</v>
       </c>
@@ -3331,7 +3331,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="68" t="s">
+      <c r="A69" s="69" t="s">
         <v>76</v>
       </c>
       <c r="B69" s="63" t="s">
@@ -3351,7 +3351,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="69"/>
+      <c r="A70" s="70"/>
       <c r="B70" s="6" t="s">
         <v>326</v>
       </c>
@@ -3365,11 +3365,11 @@
         <v>-1E-4</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>353</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="69"/>
+      <c r="A71" s="70"/>
       <c r="B71" s="17" t="s">
         <v>79</v>
       </c>
@@ -3387,7 +3387,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="70"/>
+      <c r="A72" s="71"/>
       <c r="B72" s="1" t="s">
         <v>276</v>
       </c>
@@ -3461,10 +3461,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="88" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3479,8 +3479,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="88"/>
-      <c r="B3" s="80"/>
+      <c r="A3" s="87"/>
+      <c r="B3" s="81"/>
       <c r="C3" s="13" t="s">
         <v>108</v>
       </c>
@@ -3493,8 +3493,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="88"/>
-      <c r="B4" s="80"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="81"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
       </c>
@@ -3507,8 +3507,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="88"/>
-      <c r="B5" s="80"/>
+      <c r="A5" s="87"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="13" t="s">
         <v>139</v>
       </c>
@@ -3521,8 +3521,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="88"/>
-      <c r="B6" s="80"/>
+      <c r="A6" s="87"/>
+      <c r="B6" s="81"/>
       <c r="C6" s="13" t="s">
         <v>142</v>
       </c>
@@ -3535,8 +3535,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="88"/>
-      <c r="B7" s="80"/>
+      <c r="A7" s="87"/>
+      <c r="B7" s="81"/>
       <c r="C7" s="13" t="s">
         <v>156</v>
       </c>
@@ -3549,8 +3549,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="88"/>
-      <c r="B8" s="80"/>
+      <c r="A8" s="87"/>
+      <c r="B8" s="81"/>
       <c r="C8" s="13" t="s">
         <v>198</v>
       </c>
@@ -3563,8 +3563,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
-      <c r="B9" s="80"/>
+      <c r="A9" s="87"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="13" t="s">
         <v>168</v>
       </c>
@@ -3577,8 +3577,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="80"/>
+      <c r="A10" s="87"/>
+      <c r="B10" s="81"/>
       <c r="C10" s="13" t="s">
         <v>190</v>
       </c>
@@ -3591,13 +3591,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
-      <c r="B11" s="80"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="81"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
-      <c r="B12" s="83" t="s">
+      <c r="A12" s="87"/>
+      <c r="B12" s="89" t="s">
         <v>232</v>
       </c>
       <c r="C12" s="48" t="s">
@@ -3612,8 +3612,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
-      <c r="B13" s="84"/>
+      <c r="A13" s="87"/>
+      <c r="B13" s="90"/>
       <c r="C13" s="45" t="s">
         <v>261</v>
       </c>
@@ -3626,8 +3626,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="88"/>
-      <c r="B14" s="84"/>
+      <c r="A14" s="87"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="45" t="s">
         <v>140</v>
       </c>
@@ -3640,8 +3640,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
-      <c r="B15" s="84"/>
+      <c r="A15" s="87"/>
+      <c r="B15" s="90"/>
       <c r="C15" s="45" t="s">
         <v>262</v>
       </c>
@@ -3654,8 +3654,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="88"/>
-      <c r="B16" s="84"/>
+      <c r="A16" s="87"/>
+      <c r="B16" s="90"/>
       <c r="C16" s="45" t="s">
         <v>84</v>
       </c>
@@ -3668,8 +3668,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="88"/>
-      <c r="B17" s="84"/>
+      <c r="A17" s="87"/>
+      <c r="B17" s="90"/>
       <c r="C17" s="45" t="s">
         <v>142</v>
       </c>
@@ -3682,8 +3682,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="88"/>
-      <c r="B18" s="84"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="90"/>
       <c r="C18" s="45" t="s">
         <v>156</v>
       </c>
@@ -3696,8 +3696,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="88"/>
-      <c r="B19" s="84"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="90"/>
       <c r="C19" s="45" t="s">
         <v>198</v>
       </c>
@@ -3710,8 +3710,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="88"/>
-      <c r="B20" s="84"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="90"/>
       <c r="C20" s="45" t="s">
         <v>168</v>
       </c>
@@ -3724,8 +3724,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="88"/>
-      <c r="B21" s="84"/>
+      <c r="A21" s="87"/>
+      <c r="B21" s="90"/>
       <c r="C21" s="45" t="s">
         <v>190</v>
       </c>
@@ -3738,16 +3738,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="88"/>
-      <c r="B22" s="93"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="91"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
       <c r="E22" s="53"/>
       <c r="F22" s="52"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="88"/>
-      <c r="B23" s="83" t="s">
+      <c r="A23" s="87"/>
+      <c r="B23" s="89" t="s">
         <v>297</v>
       </c>
       <c r="C23" s="45" t="s">
@@ -3762,8 +3762,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="88"/>
-      <c r="B24" s="84"/>
+      <c r="A24" s="87"/>
+      <c r="B24" s="90"/>
       <c r="C24" s="45" t="s">
         <v>108</v>
       </c>
@@ -3776,8 +3776,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="88"/>
-      <c r="B25" s="84"/>
+      <c r="A25" s="87"/>
+      <c r="B25" s="90"/>
       <c r="C25" s="45" t="s">
         <v>84</v>
       </c>
@@ -3790,8 +3790,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="88"/>
-      <c r="B26" s="84"/>
+      <c r="A26" s="87"/>
+      <c r="B26" s="90"/>
       <c r="C26" s="45" t="s">
         <v>320</v>
       </c>
@@ -3804,8 +3804,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="88"/>
-      <c r="B27" s="84"/>
+      <c r="A27" s="87"/>
+      <c r="B27" s="90"/>
       <c r="C27" s="45" t="s">
         <v>142</v>
       </c>
@@ -3818,8 +3818,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="88"/>
-      <c r="B28" s="84"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="90"/>
       <c r="C28" s="45" t="s">
         <v>156</v>
       </c>
@@ -3832,8 +3832,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="88"/>
-      <c r="B29" s="84"/>
+      <c r="A29" s="87"/>
+      <c r="B29" s="90"/>
       <c r="C29" s="45" t="s">
         <v>198</v>
       </c>
@@ -3846,8 +3846,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="88"/>
-      <c r="B30" s="84"/>
+      <c r="A30" s="87"/>
+      <c r="B30" s="90"/>
       <c r="C30" s="45" t="s">
         <v>168</v>
       </c>
@@ -3860,8 +3860,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="88"/>
-      <c r="B31" s="84"/>
+      <c r="A31" s="87"/>
+      <c r="B31" s="90"/>
       <c r="C31" s="45" t="s">
         <v>190</v>
       </c>
@@ -3874,16 +3874,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="88"/>
-      <c r="B32" s="93"/>
+      <c r="A32" s="87"/>
+      <c r="B32" s="91"/>
       <c r="C32" s="52"/>
       <c r="D32" s="52"/>
       <c r="E32" s="53"/>
       <c r="F32" s="52"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="88"/>
-      <c r="B33" s="94" t="s">
+      <c r="A33" s="87"/>
+      <c r="B33" s="92" t="s">
         <v>231</v>
       </c>
       <c r="C33" s="45" t="s">
@@ -3898,8 +3898,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="88"/>
-      <c r="B34" s="94"/>
+      <c r="A34" s="87"/>
+      <c r="B34" s="92"/>
       <c r="C34" s="45" t="s">
         <v>108</v>
       </c>
@@ -3912,8 +3912,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="88"/>
-      <c r="B35" s="94"/>
+      <c r="A35" s="87"/>
+      <c r="B35" s="92"/>
       <c r="C35" s="45" t="s">
         <v>84</v>
       </c>
@@ -3926,8 +3926,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="88"/>
-      <c r="B36" s="94"/>
+      <c r="A36" s="87"/>
+      <c r="B36" s="92"/>
       <c r="C36" s="45" t="s">
         <v>307</v>
       </c>
@@ -3940,8 +3940,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="88"/>
-      <c r="B37" s="94"/>
+      <c r="A37" s="87"/>
+      <c r="B37" s="92"/>
       <c r="C37" s="45" t="s">
         <v>274</v>
       </c>
@@ -3954,8 +3954,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="88"/>
-      <c r="B38" s="94"/>
+      <c r="A38" s="87"/>
+      <c r="B38" s="92"/>
       <c r="C38" s="45" t="s">
         <v>142</v>
       </c>
@@ -3968,8 +3968,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="88"/>
-      <c r="B39" s="94"/>
+      <c r="A39" s="87"/>
+      <c r="B39" s="92"/>
       <c r="C39" s="45" t="s">
         <v>156</v>
       </c>
@@ -3982,8 +3982,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="88"/>
-      <c r="B40" s="94"/>
+      <c r="A40" s="87"/>
+      <c r="B40" s="92"/>
       <c r="C40" s="45" t="s">
         <v>198</v>
       </c>
@@ -3996,8 +3996,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="88"/>
-      <c r="B41" s="94"/>
+      <c r="A41" s="87"/>
+      <c r="B41" s="92"/>
       <c r="C41" s="45" t="s">
         <v>168</v>
       </c>
@@ -4010,8 +4010,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="88"/>
-      <c r="B42" s="94"/>
+      <c r="A42" s="87"/>
+      <c r="B42" s="92"/>
       <c r="C42" s="45" t="s">
         <v>190</v>
       </c>
@@ -4024,15 +4024,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="88"/>
-      <c r="B43" s="94"/>
+      <c r="A43" s="87"/>
+      <c r="B43" s="92"/>
       <c r="C43" s="45"/>
       <c r="D43" s="45"/>
       <c r="E43" s="50"/>
       <c r="F43" s="45"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="87" t="s">
+      <c r="A44" s="85" t="s">
         <v>71</v>
       </c>
       <c r="B44" s="96" t="s">
@@ -4050,8 +4050,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="88"/>
-      <c r="B45" s="82"/>
+      <c r="A45" s="87"/>
+      <c r="B45" s="83"/>
       <c r="C45" s="13" t="s">
         <v>112</v>
       </c>
@@ -4064,8 +4064,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="88"/>
-      <c r="B46" s="82"/>
+      <c r="A46" s="87"/>
+      <c r="B46" s="83"/>
       <c r="C46" s="13" t="s">
         <v>136</v>
       </c>
@@ -4078,8 +4078,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="88"/>
-      <c r="B47" s="82"/>
+      <c r="A47" s="87"/>
+      <c r="B47" s="83"/>
       <c r="C47" s="13" t="s">
         <v>137</v>
       </c>
@@ -4092,8 +4092,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="88"/>
-      <c r="B48" s="82"/>
+      <c r="A48" s="87"/>
+      <c r="B48" s="83"/>
       <c r="C48" s="13" t="s">
         <v>142</v>
       </c>
@@ -4106,8 +4106,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="88"/>
-      <c r="B49" s="82"/>
+      <c r="A49" s="87"/>
+      <c r="B49" s="83"/>
       <c r="C49" s="13" t="s">
         <v>156</v>
       </c>
@@ -4120,8 +4120,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="88"/>
-      <c r="B50" s="82"/>
+      <c r="A50" s="87"/>
+      <c r="B50" s="83"/>
       <c r="C50" s="13" t="s">
         <v>198</v>
       </c>
@@ -4134,8 +4134,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="88"/>
-      <c r="B51" s="82"/>
+      <c r="A51" s="87"/>
+      <c r="B51" s="83"/>
       <c r="C51" s="13" t="s">
         <v>168</v>
       </c>
@@ -4148,8 +4148,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="88"/>
-      <c r="B52" s="82"/>
+      <c r="A52" s="87"/>
+      <c r="B52" s="83"/>
       <c r="C52" s="13" t="s">
         <v>190</v>
       </c>
@@ -4162,152 +4162,149 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="88"/>
-      <c r="B53" s="91"/>
+      <c r="A53" s="87"/>
+      <c r="B53" s="97"/>
       <c r="C53" s="37"/>
       <c r="D53" s="37"/>
       <c r="E53" s="38"/>
       <c r="F53" s="37"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="88"/>
-      <c r="B54" s="94" t="s">
+      <c r="A54" s="87"/>
+      <c r="B54" s="83" t="s">
         <v>344</v>
       </c>
-      <c r="C54" s="45" t="s">
+      <c r="C54" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="45" t="s">
+      <c r="D54" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="E54" s="47"/>
-      <c r="F54" s="45" t="s">
+      <c r="E54" s="31"/>
+      <c r="F54" s="13" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="88"/>
-      <c r="B55" s="94"/>
-      <c r="C55" s="45" t="s">
+      <c r="A55" s="87"/>
+      <c r="B55" s="83"/>
+      <c r="C55" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D55" s="45" t="s">
+      <c r="D55" s="13" t="s">
         <v>355</v>
       </c>
-      <c r="E55" s="50"/>
-      <c r="F55" s="45" t="s">
+      <c r="E55" s="33"/>
+      <c r="F55" s="13" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="88"/>
-      <c r="B56" s="94"/>
-      <c r="C56" s="45" t="s">
+      <c r="A56" s="87"/>
+      <c r="B56" s="83"/>
+      <c r="C56" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D56" s="45" t="s">
+      <c r="D56" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="E56" s="51"/>
-      <c r="F56" s="66" t="s">
-        <v>133</v>
+      <c r="E56" s="34"/>
+      <c r="F56" s="13" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="88"/>
-      <c r="B57" s="94"/>
-      <c r="C57" s="45" t="s">
+      <c r="A57" s="87"/>
+      <c r="B57" s="83"/>
+      <c r="C57" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D57" s="45" t="s">
+      <c r="D57" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="E57" s="50"/>
-      <c r="F57" s="66" t="s">
-        <v>133</v>
+      <c r="E57" s="33"/>
+      <c r="F57" s="13" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="88"/>
-      <c r="B58" s="94"/>
-      <c r="C58" s="45" t="s">
+      <c r="A58" s="87"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D58" s="45" t="s">
+      <c r="D58" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="E58" s="50"/>
-      <c r="F58" s="66" t="s">
+      <c r="E58" s="33"/>
+      <c r="F58" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="88"/>
-      <c r="B59" s="94"/>
-      <c r="C59" s="45" t="s">
+      <c r="A59" s="87"/>
+      <c r="B59" s="83"/>
+      <c r="C59" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D59" s="45" t="s">
+      <c r="D59" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="E59" s="50"/>
-      <c r="F59" s="66" t="s">
+      <c r="E59" s="33"/>
+      <c r="F59" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="88"/>
-      <c r="B60" s="94"/>
-      <c r="C60" s="45" t="s">
+      <c r="A60" s="87"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D60" s="45" t="s">
+      <c r="D60" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="E60" s="50"/>
-      <c r="F60" s="66" t="s">
+      <c r="E60" s="33"/>
+      <c r="F60" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="88"/>
-      <c r="B61" s="94"/>
-      <c r="C61" s="45" t="s">
+      <c r="A61" s="87"/>
+      <c r="B61" s="83"/>
+      <c r="C61" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="D61" s="45" t="s">
+      <c r="D61" s="13" t="s">
         <v>361</v>
       </c>
-      <c r="E61" s="50"/>
-      <c r="F61" s="66" t="s">
+      <c r="E61" s="33"/>
+      <c r="F61" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="88"/>
-      <c r="B62" s="94"/>
-      <c r="C62" s="45" t="s">
+      <c r="A62" s="87"/>
+      <c r="B62" s="83"/>
+      <c r="C62" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D62" s="45" t="s">
+      <c r="D62" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="E62" s="50"/>
-      <c r="F62" s="66" t="s">
+      <c r="E62" s="33"/>
+      <c r="F62" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="88"/>
+      <c r="A63" s="87"/>
       <c r="B63" s="97"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="50"/>
-      <c r="F63" s="45"/>
+      <c r="E63" s="33"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="88"/>
-      <c r="B64" s="90" t="s">
+      <c r="A64" s="87"/>
+      <c r="B64" s="94" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="35" t="s">
@@ -4322,8 +4319,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="88"/>
-      <c r="B65" s="82"/>
+      <c r="A65" s="87"/>
+      <c r="B65" s="83"/>
       <c r="C65" s="13" t="s">
         <v>114</v>
       </c>
@@ -4336,8 +4333,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="88"/>
-      <c r="B66" s="80"/>
+      <c r="A66" s="87"/>
+      <c r="B66" s="81"/>
       <c r="C66" s="13" t="s">
         <v>112</v>
       </c>
@@ -4350,8 +4347,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="88"/>
-      <c r="B67" s="80"/>
+      <c r="A67" s="87"/>
+      <c r="B67" s="81"/>
       <c r="C67" s="13" t="s">
         <v>108</v>
       </c>
@@ -4364,8 +4361,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="88"/>
-      <c r="B68" s="80"/>
+      <c r="A68" s="87"/>
+      <c r="B68" s="81"/>
       <c r="C68" s="13" t="s">
         <v>127</v>
       </c>
@@ -4378,8 +4375,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="88"/>
-      <c r="B69" s="80"/>
+      <c r="A69" s="87"/>
+      <c r="B69" s="81"/>
       <c r="C69" s="13" t="s">
         <v>128</v>
       </c>
@@ -4392,8 +4389,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="88"/>
-      <c r="B70" s="80"/>
+      <c r="A70" s="87"/>
+      <c r="B70" s="81"/>
       <c r="C70" s="13" t="s">
         <v>142</v>
       </c>
@@ -4406,8 +4403,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="88"/>
-      <c r="B71" s="80"/>
+      <c r="A71" s="87"/>
+      <c r="B71" s="81"/>
       <c r="C71" s="13" t="s">
         <v>156</v>
       </c>
@@ -4420,8 +4417,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="88"/>
-      <c r="B72" s="80"/>
+      <c r="A72" s="87"/>
+      <c r="B72" s="81"/>
       <c r="C72" s="13" t="s">
         <v>198</v>
       </c>
@@ -4434,8 +4431,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="88"/>
-      <c r="B73" s="80"/>
+      <c r="A73" s="87"/>
+      <c r="B73" s="81"/>
       <c r="C73" s="13" t="s">
         <v>168</v>
       </c>
@@ -4448,8 +4445,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="88"/>
-      <c r="B74" s="80"/>
+      <c r="A74" s="87"/>
+      <c r="B74" s="81"/>
       <c r="C74" s="13" t="s">
         <v>190</v>
       </c>
@@ -4462,7 +4459,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="89"/>
+      <c r="A75" s="93"/>
       <c r="B75" s="95"/>
       <c r="C75" s="41"/>
       <c r="D75" s="41"/>
@@ -4470,10 +4467,10 @@
       <c r="F75" s="41"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="87" t="s">
+      <c r="A76" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="86" t="s">
+      <c r="B76" s="88" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="26" t="s">
@@ -4488,8 +4485,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="88"/>
-      <c r="B77" s="80"/>
+      <c r="A77" s="87"/>
+      <c r="B77" s="81"/>
       <c r="C77" s="13" t="s">
         <v>154</v>
       </c>
@@ -4502,13 +4499,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="88"/>
-      <c r="B78" s="81"/>
+      <c r="A78" s="87"/>
+      <c r="B78" s="82"/>
       <c r="E78" s="31"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="88"/>
-      <c r="B79" s="90" t="s">
+      <c r="A79" s="87"/>
+      <c r="B79" s="94" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="35" t="s">
@@ -4523,8 +4520,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="88"/>
-      <c r="B80" s="82"/>
+      <c r="A80" s="87"/>
+      <c r="B80" s="83"/>
       <c r="C80" s="13" t="s">
         <v>108</v>
       </c>
@@ -4537,8 +4534,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="88"/>
-      <c r="B81" s="82"/>
+      <c r="A81" s="87"/>
+      <c r="B81" s="83"/>
       <c r="C81" s="13" t="s">
         <v>123</v>
       </c>
@@ -4551,8 +4548,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="88"/>
-      <c r="B82" s="82"/>
+      <c r="A82" s="87"/>
+      <c r="B82" s="83"/>
       <c r="C82" s="13" t="s">
         <v>142</v>
       </c>
@@ -4565,8 +4562,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="88"/>
-      <c r="B83" s="82"/>
+      <c r="A83" s="87"/>
+      <c r="B83" s="83"/>
       <c r="C83" s="13" t="s">
         <v>156</v>
       </c>
@@ -4579,8 +4576,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="88"/>
-      <c r="B84" s="82"/>
+      <c r="A84" s="87"/>
+      <c r="B84" s="83"/>
       <c r="C84" s="13" t="s">
         <v>162</v>
       </c>
@@ -4593,8 +4590,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="88"/>
-      <c r="B85" s="82"/>
+      <c r="A85" s="87"/>
+      <c r="B85" s="83"/>
       <c r="C85" s="13" t="s">
         <v>198</v>
       </c>
@@ -4607,8 +4604,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="88"/>
-      <c r="B86" s="82"/>
+      <c r="A86" s="87"/>
+      <c r="B86" s="83"/>
       <c r="C86" s="13" t="s">
         <v>168</v>
       </c>
@@ -4621,8 +4618,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="88"/>
-      <c r="B87" s="82"/>
+      <c r="A87" s="87"/>
+      <c r="B87" s="83"/>
       <c r="C87" s="13" t="s">
         <v>190</v>
       </c>
@@ -4635,12 +4632,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="88"/>
-      <c r="B88" s="91"/>
+      <c r="A88" s="87"/>
+      <c r="B88" s="97"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="88"/>
-      <c r="B89" s="90" t="s">
+      <c r="A89" s="87"/>
+      <c r="B89" s="94" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="35" t="s">
@@ -4655,8 +4652,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="88"/>
-      <c r="B90" s="82"/>
+      <c r="A90" s="87"/>
+      <c r="B90" s="83"/>
       <c r="C90" s="13" t="s">
         <v>109</v>
       </c>
@@ -4669,8 +4666,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="88"/>
-      <c r="B91" s="82"/>
+      <c r="A91" s="87"/>
+      <c r="B91" s="83"/>
       <c r="C91" s="13" t="s">
         <v>121</v>
       </c>
@@ -4683,8 +4680,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="88"/>
-      <c r="B92" s="82"/>
+      <c r="A92" s="87"/>
+      <c r="B92" s="83"/>
       <c r="C92" s="13" t="s">
         <v>142</v>
       </c>
@@ -4697,8 +4694,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="88"/>
-      <c r="B93" s="82"/>
+      <c r="A93" s="87"/>
+      <c r="B93" s="83"/>
       <c r="C93" s="13" t="s">
         <v>156</v>
       </c>
@@ -4711,8 +4708,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="88"/>
-      <c r="B94" s="82"/>
+      <c r="A94" s="87"/>
+      <c r="B94" s="83"/>
       <c r="C94" s="13" t="s">
         <v>162</v>
       </c>
@@ -4725,8 +4722,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="88"/>
-      <c r="B95" s="82"/>
+      <c r="A95" s="87"/>
+      <c r="B95" s="83"/>
       <c r="C95" s="13" t="s">
         <v>198</v>
       </c>
@@ -4739,8 +4736,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="88"/>
-      <c r="B96" s="82"/>
+      <c r="A96" s="87"/>
+      <c r="B96" s="83"/>
       <c r="C96" s="13" t="s">
         <v>168</v>
       </c>
@@ -4753,8 +4750,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="88"/>
-      <c r="B97" s="82"/>
+      <c r="A97" s="87"/>
+      <c r="B97" s="83"/>
       <c r="C97" s="13" t="s">
         <v>190</v>
       </c>
@@ -4767,14 +4764,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="89"/>
-      <c r="B98" s="92"/>
+      <c r="A98" s="93"/>
+      <c r="B98" s="99"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="87" t="s">
+      <c r="A99" s="85" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="86" t="s">
+      <c r="B99" s="88" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="26" t="s">
@@ -4789,8 +4786,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="88"/>
-      <c r="B100" s="80"/>
+      <c r="A100" s="87"/>
+      <c r="B100" s="81"/>
       <c r="C100" s="13" t="s">
         <v>230</v>
       </c>
@@ -4803,8 +4800,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="88"/>
-      <c r="B101" s="80"/>
+      <c r="A101" s="87"/>
+      <c r="B101" s="81"/>
       <c r="C101" s="13" t="s">
         <v>151</v>
       </c>
@@ -4817,16 +4814,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="88"/>
-      <c r="B102" s="81"/>
+      <c r="A102" s="87"/>
+      <c r="B102" s="82"/>
       <c r="C102" s="37"/>
       <c r="D102" s="37"/>
       <c r="E102" s="38"/>
       <c r="F102" s="37"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="88"/>
-      <c r="B103" s="79" t="s">
+      <c r="A103" s="87"/>
+      <c r="B103" s="80" t="s">
         <v>330</v>
       </c>
       <c r="C103" s="13" t="s">
@@ -4841,8 +4838,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="88"/>
-      <c r="B104" s="80"/>
+      <c r="A104" s="87"/>
+      <c r="B104" s="81"/>
       <c r="C104" s="13" t="s">
         <v>335</v>
       </c>
@@ -4855,8 +4852,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="88"/>
-      <c r="B105" s="80"/>
+      <c r="A105" s="87"/>
+      <c r="B105" s="81"/>
       <c r="C105" s="13" t="s">
         <v>336</v>
       </c>
@@ -4869,13 +4866,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="88"/>
-      <c r="B106" s="81"/>
+      <c r="A106" s="87"/>
+      <c r="B106" s="82"/>
       <c r="E106" s="33"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="88"/>
-      <c r="B107" s="79" t="s">
+      <c r="A107" s="87"/>
+      <c r="B107" s="80" t="s">
         <v>79</v>
       </c>
       <c r="C107" s="35" t="s">
@@ -4890,8 +4887,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="88"/>
-      <c r="B108" s="80"/>
+      <c r="A108" s="87"/>
+      <c r="B108" s="81"/>
       <c r="C108" s="13" t="s">
         <v>152</v>
       </c>
@@ -4904,16 +4901,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="88"/>
-      <c r="B109" s="81"/>
+      <c r="A109" s="87"/>
+      <c r="B109" s="82"/>
       <c r="C109" s="37"/>
       <c r="D109" s="37"/>
       <c r="E109" s="38"/>
       <c r="F109" s="37"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="88"/>
-      <c r="B110" s="83" t="s">
+      <c r="A110" s="87"/>
+      <c r="B110" s="89" t="s">
         <v>276</v>
       </c>
       <c r="C110" s="45" t="s">
@@ -4928,8 +4925,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="88"/>
-      <c r="B111" s="84"/>
+      <c r="A111" s="87"/>
+      <c r="B111" s="90"/>
       <c r="C111" s="45" t="s">
         <v>277</v>
       </c>
@@ -4942,18 +4939,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="89"/>
-      <c r="B112" s="85"/>
+      <c r="A112" s="93"/>
+      <c r="B112" s="98"/>
       <c r="C112" s="54"/>
       <c r="D112" s="54"/>
       <c r="E112" s="55"/>
       <c r="F112" s="54"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="87" t="s">
+      <c r="A113" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="B113" s="86" t="s">
+      <c r="B113" s="88" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="26" t="s">
@@ -4968,8 +4965,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="100"/>
-      <c r="B114" s="80"/>
+      <c r="A114" s="86"/>
+      <c r="B114" s="81"/>
       <c r="C114" s="13" t="s">
         <v>175</v>
       </c>
@@ -4981,16 +4978,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="100"/>
-      <c r="B115" s="81"/>
+      <c r="A115" s="86"/>
+      <c r="B115" s="82"/>
       <c r="C115" s="37"/>
       <c r="D115" s="37"/>
       <c r="E115" s="37"/>
       <c r="F115" s="37"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="100"/>
-      <c r="B116" s="79" t="s">
+      <c r="A116" s="86"/>
+      <c r="B116" s="80" t="s">
         <v>184</v>
       </c>
       <c r="C116" s="13" t="s">
@@ -5004,8 +5001,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="100"/>
-      <c r="B117" s="80"/>
+      <c r="A117" s="86"/>
+      <c r="B117" s="81"/>
       <c r="C117" s="13" t="s">
         <v>182</v>
       </c>
@@ -5017,8 +5014,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="100"/>
-      <c r="B118" s="80"/>
+      <c r="A118" s="86"/>
+      <c r="B118" s="81"/>
       <c r="C118" s="13" t="s">
         <v>178</v>
       </c>
@@ -5030,8 +5027,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="100"/>
-      <c r="B119" s="80"/>
+      <c r="A119" s="86"/>
+      <c r="B119" s="81"/>
       <c r="C119" s="13" t="s">
         <v>180</v>
       </c>
@@ -5043,8 +5040,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="100"/>
-      <c r="B120" s="80"/>
+      <c r="A120" s="86"/>
+      <c r="B120" s="81"/>
       <c r="C120" s="13" t="s">
         <v>183</v>
       </c>
@@ -5056,8 +5053,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="100"/>
-      <c r="B121" s="80"/>
+      <c r="A121" s="86"/>
+      <c r="B121" s="81"/>
       <c r="C121" s="13" t="s">
         <v>193</v>
       </c>
@@ -5069,12 +5066,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="100"/>
-      <c r="B122" s="80"/>
+      <c r="A122" s="86"/>
+      <c r="B122" s="81"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="100"/>
-      <c r="B123" s="79" t="s">
+      <c r="A123" s="86"/>
+      <c r="B123" s="80" t="s">
         <v>208</v>
       </c>
       <c r="C123" s="35" t="s">
@@ -5089,8 +5086,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="100"/>
-      <c r="B124" s="80"/>
+      <c r="A124" s="86"/>
+      <c r="B124" s="81"/>
       <c r="C124" s="13" t="s">
         <v>206</v>
       </c>
@@ -5102,8 +5099,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="100"/>
-      <c r="B125" s="80"/>
+      <c r="A125" s="86"/>
+      <c r="B125" s="81"/>
       <c r="C125" s="13" t="s">
         <v>217</v>
       </c>
@@ -5115,8 +5112,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="100"/>
-      <c r="B126" s="80"/>
+      <c r="A126" s="86"/>
+      <c r="B126" s="81"/>
       <c r="C126" s="13" t="s">
         <v>207</v>
       </c>
@@ -5128,8 +5125,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="100"/>
-      <c r="B127" s="80"/>
+      <c r="A127" s="86"/>
+      <c r="B127" s="81"/>
       <c r="C127" s="13" t="s">
         <v>339</v>
       </c>
@@ -5141,8 +5138,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="100"/>
-      <c r="B128" s="80"/>
+      <c r="A128" s="86"/>
+      <c r="B128" s="81"/>
       <c r="C128" s="45" t="s">
         <v>363</v>
       </c>
@@ -5155,8 +5152,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="100"/>
-      <c r="B129" s="80"/>
+      <c r="A129" s="86"/>
+      <c r="B129" s="81"/>
       <c r="C129" s="45" t="s">
         <v>365</v>
       </c>
@@ -5169,8 +5166,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="100"/>
-      <c r="B130" s="80"/>
+      <c r="A130" s="86"/>
+      <c r="B130" s="81"/>
       <c r="C130" s="13" t="s">
         <v>219</v>
       </c>
@@ -5182,8 +5179,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="100"/>
-      <c r="B131" s="80"/>
+      <c r="A131" s="86"/>
+      <c r="B131" s="81"/>
       <c r="C131" s="13" t="s">
         <v>223</v>
       </c>
@@ -5195,8 +5192,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="100"/>
-      <c r="B132" s="80"/>
+      <c r="A132" s="86"/>
+      <c r="B132" s="81"/>
       <c r="C132" s="13" t="s">
         <v>204</v>
       </c>
@@ -5208,8 +5205,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="100"/>
-      <c r="B133" s="80"/>
+      <c r="A133" s="86"/>
+      <c r="B133" s="81"/>
       <c r="C133" s="45" t="s">
         <v>280</v>
       </c>
@@ -5222,8 +5219,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="100"/>
-      <c r="B134" s="80"/>
+      <c r="A134" s="86"/>
+      <c r="B134" s="81"/>
       <c r="C134" s="45" t="s">
         <v>283</v>
       </c>
@@ -5236,16 +5233,16 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="100"/>
-      <c r="B135" s="80"/>
+      <c r="A135" s="86"/>
+      <c r="B135" s="81"/>
       <c r="C135" s="45"/>
       <c r="D135" s="45"/>
       <c r="E135" s="45"/>
       <c r="F135" s="45"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="100"/>
-      <c r="B136" s="79" t="s">
+      <c r="A136" s="86"/>
+      <c r="B136" s="80" t="s">
         <v>224</v>
       </c>
       <c r="C136" s="35" t="s">
@@ -5260,8 +5257,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="100"/>
-      <c r="B137" s="98"/>
+      <c r="A137" s="86"/>
+      <c r="B137" s="84"/>
       <c r="C137" s="13" t="s">
         <v>341</v>
       </c>
@@ -5273,8 +5270,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="100"/>
-      <c r="B138" s="98"/>
+      <c r="A138" s="86"/>
+      <c r="B138" s="84"/>
       <c r="C138" s="13" t="s">
         <v>227</v>
       </c>
@@ -5286,8 +5283,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="100"/>
-      <c r="B139" s="98"/>
+      <c r="A139" s="86"/>
+      <c r="B139" s="84"/>
       <c r="C139" s="45" t="s">
         <v>284</v>
       </c>
@@ -5300,8 +5297,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="100"/>
-      <c r="B140" s="98"/>
+      <c r="A140" s="86"/>
+      <c r="B140" s="84"/>
       <c r="C140" s="45" t="s">
         <v>286</v>
       </c>
@@ -5314,12 +5311,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="100"/>
-      <c r="B141" s="98"/>
+      <c r="A141" s="86"/>
+      <c r="B141" s="84"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="100"/>
-      <c r="B142" s="79" t="s">
+      <c r="A142" s="86"/>
+      <c r="B142" s="80" t="s">
         <v>369</v>
       </c>
       <c r="C142" s="35" t="s">
@@ -5334,21 +5331,29 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="100"/>
-      <c r="B143" s="98"/>
-      <c r="C143" s="99" t="s">
+      <c r="A143" s="86"/>
+      <c r="B143" s="84"/>
+      <c r="C143" s="68" t="s">
         <v>372</v>
       </c>
-      <c r="D143" s="99" t="s">
+      <c r="D143" s="68" t="s">
         <v>373</v>
       </c>
-      <c r="E143" s="99"/>
-      <c r="F143" s="99" t="s">
+      <c r="E143" s="68"/>
+      <c r="F143" s="68" t="s">
         <v>299</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -5365,14 +5370,6 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
-    <mergeCell ref="B136:B141"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A549A5-5F77-40F2-ACF9-C45F1E478AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47290517-900B-4D72-89DA-3AA8C27A191E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -480,9 +480,6 @@
     <t>€/kWa</t>
   </si>
   <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
     <t>(%_Kapa)/h</t>
   </si>
   <si>
@@ -765,9 +762,6 @@
     <t>kW_el</t>
   </si>
   <si>
-    <t>€ h / kg a</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -1297,6 +1291,12 @@
   </si>
   <si>
     <t>kWh_th/a</t>
+  </si>
+  <si>
+    <t>€/ kg a</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -1450,45 +1450,49 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1496,33 +1500,29 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1861,7 +1861,7 @@
     <col min="2" max="2" width="18.6640625" style="6" customWidth="1"/>
     <col min="3" max="3" width="36.21875" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.77734375" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.77734375" style="7" customWidth="1"/>
@@ -1893,51 +1893,51 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="9">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="7" t="s">
         <v>84</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="10">
         <v>50</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="11">
         <v>1000</v>
       </c>
       <c r="F4" s="7" t="s">
@@ -1945,15 +1945,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="12">
         <v>0.03</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -1961,15 +1961,15 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="13">
         <v>20</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -1977,15 +1977,15 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="40"/>
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="12">
         <v>0.08</v>
       </c>
       <c r="F7" s="7" t="s">
@@ -1993,33 +1993,33 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="18" t="s">
+      <c r="A8" s="33"/>
+      <c r="B8" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>234</v>
-      </c>
-      <c r="E8" s="20">
+      <c r="E8" s="15">
         <v>1.5</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>233</v>
+      <c r="F8" s="14" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="40"/>
       <c r="C9" s="7" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="E9" s="14">
+        <v>233</v>
+      </c>
+      <c r="E9" s="10">
         <v>285.39999999999998</v>
       </c>
       <c r="F9" s="7" t="s">
@@ -2027,31 +2027,31 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="40"/>
       <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="14">
+        <v>234</v>
+      </c>
+      <c r="E10" s="10">
         <v>5110</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>241</v>
+      <c r="F10" s="10" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="E11" s="16">
+        <v>235</v>
+      </c>
+      <c r="E11" s="12">
         <v>0.05</v>
       </c>
       <c r="F11" s="7" t="s">
@@ -2059,47 +2059,47 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="14">
+        <v>236</v>
+      </c>
+      <c r="E12" s="10">
         <v>0.189</v>
       </c>
       <c r="F12" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="33"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" s="10">
+        <v>1.375</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="E13" s="14">
-        <v>1.375</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="17">
+        <v>237</v>
+      </c>
+      <c r="E14" s="13">
         <v>25</v>
       </c>
       <c r="F14" s="7" t="s">
@@ -2107,81 +2107,81 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="22" t="s">
+      <c r="A15" s="33"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="E15" s="23">
+      <c r="D15" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E15" s="17">
         <v>0.08</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-      <c r="B16" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="33"/>
+      <c r="B16" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="E16" s="24">
+      <c r="D16" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="E16" s="18">
         <v>3.7</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="40"/>
       <c r="C17" s="7" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="E17" s="16">
+        <v>290</v>
+      </c>
+      <c r="E17" s="12">
         <v>0.27</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
+      <c r="A18" s="33"/>
+      <c r="B18" s="40"/>
       <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="E18" s="16">
+        <v>291</v>
+      </c>
+      <c r="E18" s="12">
         <v>700</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
+      <c r="A19" s="33"/>
+      <c r="B19" s="40"/>
       <c r="C19" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="E19" s="16">
+        <v>292</v>
+      </c>
+      <c r="E19" s="12">
         <v>0.02</v>
       </c>
       <c r="F19" s="7" t="s">
@@ -2189,15 +2189,15 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="40"/>
       <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="E20" s="16">
+        <v>293</v>
+      </c>
+      <c r="E20" s="12">
         <v>20</v>
       </c>
       <c r="F20" s="7" t="s">
@@ -2205,81 +2205,81 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="22" t="s">
+      <c r="A21" s="33"/>
+      <c r="B21" s="44"/>
+      <c r="C21" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="22" t="s">
-        <v>296</v>
-      </c>
-      <c r="E21" s="23">
+      <c r="D21" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="E21" s="17">
         <v>0.05</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
-      <c r="B22" s="25" t="s">
-        <v>231</v>
+      <c r="A22" s="33"/>
+      <c r="B22" s="36" t="s">
+        <v>229</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="E22" s="14">
+        <v>243</v>
+      </c>
+      <c r="E22" s="10">
         <v>0.5</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="25"/>
+      <c r="A23" s="33"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="10">
+        <v>1.75</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="E23" s="14">
-        <v>1.75</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="25"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="E24" s="14">
+        <v>244</v>
+      </c>
+      <c r="E24" s="10">
         <v>7000</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="25"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="36"/>
       <c r="C25" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="E25" s="16">
+        <v>245</v>
+      </c>
+      <c r="E25" s="12">
         <v>0.05</v>
       </c>
       <c r="F25" s="7" t="s">
@@ -2287,15 +2287,15 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="25"/>
+      <c r="A26" s="33"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E26" s="17">
+        <v>246</v>
+      </c>
+      <c r="E26" s="13">
         <v>15</v>
       </c>
       <c r="F26" s="7" t="s">
@@ -2303,15 +2303,15 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="12"/>
-      <c r="B27" s="25"/>
+      <c r="A27" s="33"/>
+      <c r="B27" s="36"/>
       <c r="C27" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="E27" s="16">
+        <v>247</v>
+      </c>
+      <c r="E27" s="12">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F27" s="7" t="s">
@@ -2319,35 +2319,35 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="19">
         <v>490</v>
       </c>
-      <c r="F28" s="10" t="s">
-        <v>93</v>
+      <c r="F28" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="12"/>
-      <c r="B29" s="25"/>
+      <c r="A29" s="33"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="12">
         <v>0.01</v>
       </c>
       <c r="F29" s="7" t="s">
@@ -2355,15 +2355,15 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="12"/>
-      <c r="B30" s="25"/>
+      <c r="A30" s="33"/>
+      <c r="B30" s="36"/>
       <c r="C30" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="13">
         <v>20</v>
       </c>
       <c r="F30" s="7" t="s">
@@ -2371,31 +2371,31 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
-      <c r="B31" s="25"/>
+      <c r="A31" s="33"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="20">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
-      <c r="B32" s="25"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="12">
         <v>0.83299999999999996</v>
       </c>
       <c r="F32" s="7" t="s">
@@ -2403,15 +2403,15 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="12"/>
-      <c r="B33" s="25"/>
+      <c r="A33" s="33"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="12">
         <v>0.83299999999999996</v>
       </c>
       <c r="F33" s="7" t="s">
@@ -2419,15 +2419,15 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
-      <c r="B34" s="25"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="12">
         <v>0.05</v>
       </c>
       <c r="F34" s="7" t="s">
@@ -2435,49 +2435,49 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="12"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="22" t="s">
+      <c r="A35" s="33"/>
+      <c r="B35" s="37"/>
+      <c r="C35" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="17">
         <v>0</v>
       </c>
-      <c r="F35" s="22" t="s">
-        <v>95</v>
+      <c r="F35" s="16" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="12"/>
-      <c r="B36" s="30" t="s">
-        <v>335</v>
-      </c>
-      <c r="C36" s="10" t="s">
+      <c r="A36" s="33"/>
+      <c r="B36" s="38" t="s">
+        <v>333</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>336</v>
-      </c>
-      <c r="E36" s="27">
+      <c r="D36" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E36" s="19">
         <v>2.83</v>
       </c>
-      <c r="F36" s="10" t="s">
-        <v>344</v>
+      <c r="F36" s="8" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="25"/>
+      <c r="A37" s="33"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E37" s="16">
+        <v>335</v>
+      </c>
+      <c r="E37" s="12">
         <v>0.03</v>
       </c>
       <c r="F37" s="7" t="s">
@@ -2485,15 +2485,15 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="12"/>
-      <c r="B38" s="25"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="E38" s="17">
+        <v>336</v>
+      </c>
+      <c r="E38" s="13">
         <v>30</v>
       </c>
       <c r="F38" s="7" t="s">
@@ -2501,31 +2501,31 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
-      <c r="B39" s="25"/>
+      <c r="A39" s="33"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="7" t="s">
         <v>20</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="E39" s="16">
+        <v>337</v>
+      </c>
+      <c r="E39" s="12">
         <v>7.3999999999999999E-4</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="25"/>
+      <c r="A40" s="33"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E40" s="16">
+        <v>338</v>
+      </c>
+      <c r="E40" s="12">
         <v>0.98</v>
       </c>
       <c r="F40" s="7" t="s">
@@ -2533,15 +2533,15 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
-      <c r="B41" s="25"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="E41" s="16">
+        <v>339</v>
+      </c>
+      <c r="E41" s="12">
         <v>0.98</v>
       </c>
       <c r="F41" s="7" t="s">
@@ -2549,15 +2549,15 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="12"/>
-      <c r="B42" s="25"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="E42" s="16">
+        <v>340</v>
+      </c>
+      <c r="E42" s="12">
         <v>0.05</v>
       </c>
       <c r="F42" s="7" t="s">
@@ -2565,49 +2565,49 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="12"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="22" t="s">
+      <c r="A43" s="33"/>
+      <c r="B43" s="36"/>
+      <c r="C43" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="22" t="s">
-        <v>343</v>
-      </c>
-      <c r="E43" s="23">
+      <c r="D43" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="E43" s="17">
         <v>0</v>
       </c>
-      <c r="F43" s="22" t="s">
+      <c r="F43" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="33"/>
+      <c r="B44" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E44" s="18">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F44" s="14" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="12"/>
-      <c r="B44" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="24">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>96</v>
-      </c>
-    </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="13"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="40"/>
       <c r="C45" s="7" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E45" s="14">
+      <c r="E45" s="10">
         <f>E46*4</f>
         <v>424</v>
       </c>
@@ -2616,15 +2616,15 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="40"/>
       <c r="C46" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D46" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="10">
         <v>106</v>
       </c>
       <c r="F46" s="7" t="s">
@@ -2632,15 +2632,15 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
-      <c r="B47" s="13"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="40"/>
       <c r="C47" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="12">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="F47" s="7" t="s">
@@ -2648,15 +2648,15 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="13"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="40"/>
       <c r="C48" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E48" s="16">
+      <c r="E48" s="12">
         <v>0.93500000000000005</v>
       </c>
       <c r="F48" s="7" t="s">
@@ -2664,15 +2664,15 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
-      <c r="B49" s="13"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="40"/>
       <c r="C49" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E49" s="16">
+      <c r="E49" s="12">
         <v>0.93500000000000005</v>
       </c>
       <c r="F49" s="7" t="s">
@@ -2680,15 +2680,15 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
-      <c r="B50" s="13"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="40"/>
       <c r="C50" s="7" t="s">
         <v>89</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="14">
+      <c r="E50" s="10">
         <v>0.25</v>
       </c>
       <c r="F50" s="7" t="s">
@@ -2696,31 +2696,31 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="13"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="40"/>
       <c r="C51" s="7" t="s">
         <v>88</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E51" s="16">
+      <c r="E51" s="12">
         <v>0</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
-      <c r="B52" s="13"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="40"/>
       <c r="C52" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E52" s="17">
+      <c r="E52" s="13">
         <v>15</v>
       </c>
       <c r="F52" s="7" t="s">
@@ -2728,62 +2728,62 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="31"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="33" t="s">
+      <c r="A53" s="34"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D53" s="33" t="s">
+      <c r="D53" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="22">
         <v>0.1</v>
       </c>
-      <c r="F53" s="33" t="s">
+      <c r="F53" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="19">
         <v>2000</v>
       </c>
-      <c r="F54" s="10" t="s">
+      <c r="F54" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
-      <c r="B55" s="30" t="s">
+      <c r="A55" s="33"/>
+      <c r="B55" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="19" t="s">
+      <c r="D55" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E55" s="24">
+      <c r="E55" s="18">
         <v>0.99</v>
       </c>
-      <c r="F55" s="19" t="s">
+      <c r="F55" s="14" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="12"/>
-      <c r="B56" s="25"/>
+      <c r="A56" s="33"/>
+      <c r="B56" s="36"/>
       <c r="C56" s="7" t="s">
         <v>10</v>
       </c>
@@ -2798,8 +2798,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
-      <c r="B57" s="25"/>
+      <c r="A57" s="33"/>
+      <c r="B57" s="36"/>
       <c r="C57" s="7" t="s">
         <v>17</v>
       </c>
@@ -2814,15 +2814,15 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="12"/>
-      <c r="B58" s="25"/>
+      <c r="A58" s="33"/>
+      <c r="B58" s="36"/>
       <c r="C58" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D58" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E58" s="14">
+      <c r="E58" s="10">
         <v>0</v>
       </c>
       <c r="F58" s="7" t="s">
@@ -2830,15 +2830,15 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
-      <c r="B59" s="25"/>
+      <c r="A59" s="33"/>
+      <c r="B59" s="36"/>
       <c r="C59" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E59" s="17">
+      <c r="E59" s="13">
         <v>25</v>
       </c>
       <c r="F59" s="7" t="s">
@@ -2846,15 +2846,15 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
-      <c r="B60" s="25"/>
+      <c r="A60" s="33"/>
+      <c r="B60" s="36"/>
       <c r="C60" s="7" t="s">
         <v>68</v>
       </c>
       <c r="D60" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E60" s="14">
+      <c r="E60" s="10">
         <v>1000000</v>
       </c>
       <c r="F60" s="7" t="s">
@@ -2862,42 +2862,42 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="12"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="22" t="s">
+      <c r="A61" s="33"/>
+      <c r="B61" s="37"/>
+      <c r="C61" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E61" s="23">
+      <c r="E61" s="17">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F61" s="22" t="s">
+      <c r="F61" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
-      <c r="B62" s="30" t="s">
+      <c r="A62" s="33"/>
+      <c r="B62" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D62" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E62" s="24">
+      <c r="E62" s="18">
         <v>0.997</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F62" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="25"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="36"/>
       <c r="C63" s="7" t="s">
         <v>10</v>
       </c>
@@ -2912,8 +2912,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="25"/>
+      <c r="A64" s="33"/>
+      <c r="B64" s="36"/>
       <c r="C64" s="7" t="s">
         <v>17</v>
       </c>
@@ -2928,8 +2928,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
-      <c r="B65" s="25"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="36"/>
       <c r="C65" s="7" t="s">
         <v>18</v>
       </c>
@@ -2944,15 +2944,15 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="25"/>
+      <c r="A66" s="33"/>
+      <c r="B66" s="36"/>
       <c r="C66" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E66" s="17">
+      <c r="E66" s="13">
         <v>25</v>
       </c>
       <c r="F66" s="7" t="s">
@@ -2960,15 +2960,15 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
-      <c r="B67" s="25"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="36"/>
       <c r="C67" s="7" t="s">
         <v>68</v>
       </c>
       <c r="D67" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E67" s="36">
+      <c r="E67" s="24">
         <v>1000000</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -2976,93 +2976,93 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="31"/>
-      <c r="B68" s="37"/>
-      <c r="C68" s="33" t="s">
+      <c r="A68" s="34"/>
+      <c r="B68" s="39"/>
+      <c r="C68" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D68" s="33" t="s">
+      <c r="D68" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="22">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F68" s="33" t="s">
+      <c r="F68" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="38" t="s">
+      <c r="B69" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="39" t="s">
+      <c r="C69" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="D69" s="39" t="s">
+      <c r="D69" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="40">
+      <c r="E69" s="27">
         <v>-1E-4</v>
       </c>
-      <c r="F69" s="39" t="s">
+      <c r="F69" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="12"/>
+      <c r="A70" s="33"/>
       <c r="B70" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="E70" s="16">
+      <c r="E70" s="12">
         <v>-1E-4</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
-      <c r="B71" s="41" t="s">
+      <c r="A71" s="33"/>
+      <c r="B71" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C71" s="42" t="s">
+      <c r="C71" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D71" s="42" t="s">
+      <c r="D71" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="E71" s="43">
+      <c r="E71" s="30">
         <v>-1.5</v>
       </c>
-      <c r="F71" s="42" t="s">
+      <c r="F71" s="29" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="31"/>
+      <c r="A72" s="34"/>
       <c r="B72" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C72" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="D72" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="C72" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="E72" s="34">
+      <c r="D72" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="E72" s="22">
         <v>-0.6</v>
       </c>
-      <c r="F72" s="33" t="s">
-        <v>290</v>
+      <c r="F72" s="21" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -3122,1069 +3122,1069 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="9"/>
+      <c r="F2" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="10" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="14"/>
+        <v>115</v>
+      </c>
+      <c r="E3" s="10"/>
       <c r="F3" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="15"/>
+        <v>123</v>
+      </c>
+      <c r="E4" s="11"/>
       <c r="F4" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="33"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="33"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="F7" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="33"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="33"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="13"/>
+      <c r="F9" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="33"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="13"/>
+      <c r="F10" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="33"/>
+      <c r="B11" s="40"/>
+      <c r="E11" s="12"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="33"/>
+      <c r="B12" s="43" t="s">
+        <v>230</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="33"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="33"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="E11" s="16"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="18" t="s">
-        <v>232</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="19" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="7" t="s">
+      <c r="D14" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="33"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="12"/>
+      <c r="F15" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="7" t="s">
-        <v>265</v>
-      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-      <c r="B16" s="13"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="40"/>
       <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="33"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="33"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="E18" s="13"/>
+      <c r="F18" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="33"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="7" t="s">
+      <c r="E19" s="13"/>
+      <c r="F19" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="33"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="E20" s="13"/>
+      <c r="F20" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="33"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="E21" s="17"/>
+      <c r="E21" s="13"/>
       <c r="F21" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="12"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="22"/>
+      <c r="A22" s="33"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="18" t="s">
-        <v>288</v>
+      <c r="A23" s="33"/>
+      <c r="B23" s="43" t="s">
+        <v>286</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E23" s="14"/>
+        <v>299</v>
+      </c>
+      <c r="E23" s="10"/>
       <c r="F23" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="13"/>
+      <c r="A24" s="33"/>
+      <c r="B24" s="40"/>
       <c r="C24" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E24" s="14"/>
+        <v>300</v>
+      </c>
+      <c r="E24" s="10"/>
       <c r="F24" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="13"/>
+      <c r="A25" s="33"/>
+      <c r="B25" s="40"/>
       <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="F25" s="7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="33"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="E26" s="13"/>
+      <c r="F26" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="33"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E27" s="13"/>
+      <c r="F27" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="33"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E25" s="16"/>
-      <c r="F25" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="7" t="s">
+      <c r="E28" s="13"/>
+      <c r="F28" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="33"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="12"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="E29" s="13"/>
+      <c r="F29" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="33"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="E28" s="17"/>
-      <c r="F28" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D29" s="7" t="s">
+      <c r="E30" s="12"/>
+      <c r="F30" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="33"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="E29" s="17"/>
-      <c r="F29" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="12"/>
       <c r="F31" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="22"/>
+      <c r="A32" s="33"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="12"/>
-      <c r="B33" s="25" t="s">
-        <v>231</v>
+      <c r="A33" s="33"/>
+      <c r="B33" s="36" t="s">
+        <v>229</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E33" s="14"/>
+        <v>264</v>
+      </c>
+      <c r="E33" s="10"/>
       <c r="F33" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
-      <c r="B34" s="25"/>
+      <c r="A34" s="33"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="E34" s="14"/>
+        <v>265</v>
+      </c>
+      <c r="E34" s="10"/>
       <c r="F34" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
-      <c r="B35" s="25"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="7" t="s">
         <v>84</v>
       </c>
       <c r="D35" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="33"/>
+      <c r="B36" s="36"/>
+      <c r="C36" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E36" s="12"/>
+      <c r="F36" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="33"/>
+      <c r="B37" s="36"/>
+      <c r="C37" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="33"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="33"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="12"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="E37" s="17"/>
-      <c r="F37" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="12"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" s="7" t="s">
+      <c r="E39" s="13"/>
+      <c r="F39" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="33"/>
+      <c r="B40" s="36"/>
+      <c r="C40" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E38" s="17"/>
-      <c r="F38" s="7" t="s">
+      <c r="E40" s="13"/>
+      <c r="F40" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="33"/>
+      <c r="B41" s="36"/>
+      <c r="C41" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E41" s="12"/>
+      <c r="F41" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="33"/>
+      <c r="B42" s="36"/>
+      <c r="C42" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E42" s="12"/>
+      <c r="F42" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="33"/>
+      <c r="B43" s="36"/>
+      <c r="E43" s="12"/>
+    </row>
+    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" s="19"/>
+      <c r="F44" s="8" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="33"/>
+      <c r="B45" s="36"/>
+      <c r="C45" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="12"/>
+      <c r="F45" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="33"/>
+      <c r="B46" s="36"/>
+      <c r="C46" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E46" s="13"/>
+      <c r="F46" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="33"/>
+      <c r="B47" s="36"/>
+      <c r="C47" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E47" s="12"/>
+      <c r="F47" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="33"/>
+      <c r="B48" s="36"/>
+      <c r="C48" s="7" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="E39" s="17"/>
-      <c r="F39" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="E40" s="17"/>
-      <c r="F40" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="E41" s="16"/>
-      <c r="F41" s="7" t="s">
+      <c r="D48" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E48" s="12"/>
+      <c r="F48" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="33"/>
+      <c r="B49" s="36"/>
+      <c r="C49" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" s="12"/>
+      <c r="F49" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="33"/>
+      <c r="B50" s="36"/>
+      <c r="C50" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E50" s="12"/>
+      <c r="F50" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="33"/>
+      <c r="B51" s="36"/>
+      <c r="C51" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" s="12"/>
+      <c r="F51" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="33"/>
+      <c r="B52" s="36"/>
+      <c r="C52" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E52" s="12"/>
+      <c r="F52" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="33"/>
+      <c r="B53" s="37"/>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="16"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="33"/>
+      <c r="B54" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E54" s="10"/>
+      <c r="F54" s="7" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="33"/>
+      <c r="B55" s="36"/>
+      <c r="C55" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="E55" s="12"/>
+      <c r="F55" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="33"/>
+      <c r="B56" s="36"/>
+      <c r="C56" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E56" s="13"/>
+      <c r="F56" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="33"/>
+      <c r="B57" s="36"/>
+      <c r="C57" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E57" s="12"/>
+      <c r="F57" s="7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="33"/>
+      <c r="B58" s="36"/>
+      <c r="C58" s="7" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="12"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="12"/>
-      <c r="B43" s="25"/>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="10" t="s">
+      <c r="D58" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E58" s="12"/>
+      <c r="F58" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="33"/>
+      <c r="B59" s="36"/>
+      <c r="C59" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E59" s="12"/>
+      <c r="F59" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="33"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E60" s="12"/>
+      <c r="F60" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="33"/>
+      <c r="B61" s="36"/>
+      <c r="C61" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="E61" s="12"/>
+      <c r="F61" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="33"/>
+      <c r="B62" s="36"/>
+      <c r="C62" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="E62" s="12"/>
+      <c r="F62" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="33"/>
+      <c r="B63" s="37"/>
+      <c r="E63" s="12"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="33"/>
+      <c r="B64" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E64" s="18"/>
+      <c r="F64" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="33"/>
+      <c r="B65" s="36"/>
+      <c r="C65" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E65" s="12"/>
+      <c r="F65" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="33"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E66" s="10"/>
+      <c r="F66" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D44" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" s="27"/>
-      <c r="F44" s="10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E45" s="16"/>
-      <c r="F45" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="17"/>
-      <c r="F46" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" s="16"/>
-      <c r="F47" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" s="16"/>
-      <c r="F48" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="E49" s="16"/>
-      <c r="F49" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E50" s="16"/>
-      <c r="F50" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E51" s="16"/>
-      <c r="F51" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E52" s="16"/>
-      <c r="F52" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="12"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="22"/>
-      <c r="D53" s="22"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="22"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="12"/>
-      <c r="B54" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="E54" s="14"/>
-      <c r="F54" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="E55" s="16"/>
-      <c r="F55" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="12"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="E56" s="17"/>
-      <c r="F56" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="E57" s="16"/>
-      <c r="F57" s="7" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="12"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="12"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="29"/>
-      <c r="E63" s="16"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="E64" s="24"/>
-      <c r="F64" s="19" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E65" s="16"/>
-      <c r="F65" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E66" s="14"/>
-      <c r="F66" s="7" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
-      <c r="B67" s="13"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="40"/>
       <c r="C67" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="14"/>
+        <v>185</v>
+      </c>
+      <c r="E67" s="10"/>
       <c r="F67" s="7" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="12"/>
-      <c r="B68" s="13"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="40"/>
       <c r="C68" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" s="10"/>
+      <c r="F68" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="33"/>
+      <c r="B69" s="40"/>
+      <c r="C69" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="D69" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="14"/>
-      <c r="F68" s="7" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="12"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="E69" s="16"/>
+      <c r="E69" s="12"/>
       <c r="F69" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="12"/>
-      <c r="B70" s="13"/>
+      <c r="A70" s="33"/>
+      <c r="B70" s="40"/>
       <c r="C70" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E70" s="14"/>
+        <v>145</v>
+      </c>
+      <c r="E70" s="10"/>
       <c r="F70" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
-      <c r="B71" s="13"/>
+      <c r="A71" s="33"/>
+      <c r="B71" s="40"/>
       <c r="C71" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E71" s="16"/>
+        <v>157</v>
+      </c>
+      <c r="E71" s="12"/>
       <c r="F71" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="12"/>
-      <c r="B72" s="13"/>
+      <c r="A72" s="33"/>
+      <c r="B72" s="40"/>
       <c r="C72" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="E72" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="E72" s="12"/>
       <c r="F72" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="12"/>
-      <c r="B73" s="13"/>
+      <c r="A73" s="33"/>
+      <c r="B73" s="40"/>
       <c r="C73" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E73" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="E73" s="12"/>
       <c r="F73" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="12"/>
-      <c r="B74" s="13"/>
+      <c r="A74" s="33"/>
+      <c r="B74" s="40"/>
       <c r="C74" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="E74" s="16"/>
+        <v>192</v>
+      </c>
+      <c r="E74" s="12"/>
       <c r="F74" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="31"/>
-      <c r="B75" s="32"/>
-      <c r="C75" s="33"/>
-      <c r="D75" s="33"/>
-      <c r="E75" s="34"/>
-      <c r="F75" s="33"/>
+      <c r="A75" s="34"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="21"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C76" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E76" s="19"/>
+      <c r="F76" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D76" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E76" s="27"/>
-      <c r="F76" s="10" t="s">
-        <v>119</v>
-      </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="12"/>
-      <c r="B77" s="13"/>
+      <c r="A77" s="33"/>
+      <c r="B77" s="40"/>
       <c r="C77" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="E77" s="14"/>
+        <v>152</v>
+      </c>
+      <c r="E77" s="10"/>
       <c r="F77" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="12"/>
-      <c r="B78" s="21"/>
-      <c r="E78" s="14"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="44"/>
+      <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="12"/>
-      <c r="B79" s="30" t="s">
+      <c r="A79" s="33"/>
+      <c r="B79" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="C79" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E79" s="24"/>
-      <c r="F79" s="19" t="s">
+      <c r="C79" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D79" s="14" t="s">
         <v>99</v>
       </c>
+      <c r="E79" s="18"/>
+      <c r="F79" s="14" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="12"/>
-      <c r="B80" s="25"/>
+      <c r="A80" s="33"/>
+      <c r="B80" s="36"/>
       <c r="C80" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="7" t="s">
@@ -4192,131 +4192,131 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="12"/>
-      <c r="B81" s="25"/>
+      <c r="A81" s="33"/>
+      <c r="B81" s="36"/>
       <c r="C81" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="12"/>
-      <c r="B82" s="25"/>
+      <c r="A82" s="33"/>
+      <c r="B82" s="36"/>
       <c r="C82" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="E82" s="14"/>
+        <v>144</v>
+      </c>
+      <c r="E82" s="10"/>
       <c r="F82" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="12"/>
-      <c r="B83" s="25"/>
+      <c r="A83" s="33"/>
+      <c r="B83" s="36"/>
       <c r="C83" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D83" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D83" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E83" s="17"/>
+      <c r="E83" s="13"/>
       <c r="F83" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="12"/>
-      <c r="B84" s="25"/>
+      <c r="A84" s="33"/>
+      <c r="B84" s="36"/>
       <c r="C84" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="D84" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E84" s="14"/>
+      <c r="E84" s="10"/>
       <c r="F84" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="12"/>
-      <c r="B85" s="25"/>
+      <c r="A85" s="33"/>
+      <c r="B85" s="36"/>
       <c r="C85" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D85" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="D85" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E85" s="14"/>
+      <c r="E85" s="10"/>
       <c r="F85" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="12"/>
-      <c r="B86" s="25"/>
+      <c r="A86" s="33"/>
+      <c r="B86" s="36"/>
       <c r="C86" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="E86" s="16"/>
+        <v>169</v>
+      </c>
+      <c r="E86" s="12"/>
       <c r="F86" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="12"/>
-      <c r="B87" s="25"/>
+      <c r="A87" s="33"/>
+      <c r="B87" s="36"/>
       <c r="C87" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D87" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="D87" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E87" s="16"/>
+      <c r="E87" s="12"/>
       <c r="F87" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="12"/>
-      <c r="B88" s="29"/>
+      <c r="A88" s="33"/>
+      <c r="B88" s="37"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="12"/>
-      <c r="B89" s="30" t="s">
+      <c r="A89" s="33"/>
+      <c r="B89" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C89" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D89" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="19" t="s">
-        <v>99</v>
+      <c r="C89" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D89" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E89" s="18"/>
+      <c r="F89" s="14" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="12"/>
-      <c r="B90" s="25"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="36"/>
       <c r="C90" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="7" t="s">
@@ -4324,676 +4324,684 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="12"/>
-      <c r="B91" s="25"/>
+      <c r="A91" s="33"/>
+      <c r="B91" s="36"/>
       <c r="C91" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="12"/>
-      <c r="B92" s="25"/>
+      <c r="A92" s="33"/>
+      <c r="B92" s="36"/>
       <c r="C92" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D92" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>143</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="12"/>
-      <c r="B93" s="25"/>
+      <c r="A93" s="33"/>
+      <c r="B93" s="36"/>
       <c r="C93" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E93" s="17"/>
+        <v>154</v>
+      </c>
+      <c r="E93" s="13"/>
       <c r="F93" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="33"/>
+      <c r="B94" s="36"/>
+      <c r="C94" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E94" s="24"/>
+      <c r="F94" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="33"/>
+      <c r="B95" s="36"/>
+      <c r="C95" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E95" s="24"/>
+      <c r="F95" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="33"/>
+      <c r="B96" s="36"/>
+      <c r="C96" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E96" s="12"/>
+      <c r="F96" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="33"/>
+      <c r="B97" s="36"/>
+      <c r="C97" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="E97" s="12"/>
+      <c r="F97" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="34"/>
+      <c r="B98" s="39"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B99" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E99" s="9"/>
+      <c r="F99" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="33"/>
+      <c r="B100" s="40"/>
+      <c r="C100" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E100" s="12"/>
+      <c r="F100" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="33"/>
+      <c r="B101" s="40"/>
+      <c r="C101" s="7" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="12"/>
-      <c r="B94" s="25"/>
-      <c r="C94" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E94" s="36"/>
-      <c r="F94" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="12"/>
-      <c r="B95" s="25"/>
-      <c r="C95" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="E95" s="36"/>
-      <c r="F95" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="12"/>
-      <c r="B96" s="25"/>
-      <c r="C96" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E96" s="16"/>
-      <c r="F96" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="12"/>
-      <c r="B97" s="25"/>
-      <c r="C97" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D97" s="7" t="s">
+      <c r="D101" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E101" s="12"/>
+      <c r="F101" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="33"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="16"/>
+      <c r="D102" s="16"/>
+      <c r="E102" s="17"/>
+      <c r="F102" s="16"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="33"/>
+      <c r="B103" s="43" t="s">
+        <v>319</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E103" s="12"/>
+      <c r="F103" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="33"/>
+      <c r="B104" s="40"/>
+      <c r="C104" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E104" s="12"/>
+      <c r="F104" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="33"/>
+      <c r="B105" s="40"/>
+      <c r="C105" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E105" s="12"/>
+      <c r="F105" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="33"/>
+      <c r="B106" s="44"/>
+      <c r="E106" s="12"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="33"/>
+      <c r="B107" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E107" s="18"/>
+      <c r="F107" s="14" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="33"/>
+      <c r="B108" s="40"/>
+      <c r="C108" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E108" s="12"/>
+      <c r="F108" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="33"/>
+      <c r="B109" s="44"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="16"/>
+      <c r="E109" s="17"/>
+      <c r="F109" s="16"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="33"/>
+      <c r="B110" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E110" s="12"/>
+      <c r="F110" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="33"/>
+      <c r="B111" s="40"/>
+      <c r="C111" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E111" s="12"/>
+      <c r="F111" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="34"/>
+      <c r="B112" s="41"/>
+      <c r="C112" s="21"/>
+      <c r="D112" s="21"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="21"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="B113" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E113" s="8"/>
+      <c r="F113" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="46"/>
+      <c r="B114" s="40"/>
+      <c r="C114" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="46"/>
+      <c r="B115" s="44"/>
+      <c r="C115" s="16"/>
+      <c r="D115" s="16"/>
+      <c r="E115" s="16"/>
+      <c r="F115" s="16"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="46"/>
+      <c r="B116" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="46"/>
+      <c r="B117" s="40"/>
+      <c r="C117" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="46"/>
+      <c r="B118" s="40"/>
+      <c r="C118" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="46"/>
+      <c r="B119" s="40"/>
+      <c r="C119" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="46"/>
+      <c r="B120" s="40"/>
+      <c r="C120" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="46"/>
+      <c r="B121" s="40"/>
+      <c r="C121" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="E97" s="16"/>
-      <c r="F97" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="31"/>
-      <c r="B98" s="37"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B99" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="E99" s="11"/>
-      <c r="F99" s="10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="12"/>
-      <c r="B100" s="13"/>
-      <c r="C100" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="E100" s="16"/>
-      <c r="F100" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="12"/>
-      <c r="B101" s="13"/>
-      <c r="C101" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E101" s="16"/>
-      <c r="F101" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="12"/>
-      <c r="B102" s="21"/>
-      <c r="C102" s="22"/>
-      <c r="D102" s="22"/>
-      <c r="E102" s="23"/>
-      <c r="F102" s="22"/>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="12"/>
-      <c r="B103" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="E103" s="16"/>
-      <c r="F103" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="12"/>
-      <c r="B104" s="13"/>
-      <c r="C104" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="E104" s="16"/>
-      <c r="F104" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="12"/>
-      <c r="B105" s="13"/>
-      <c r="C105" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="E105" s="16"/>
-      <c r="F105" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="12"/>
-      <c r="B106" s="21"/>
-      <c r="E106" s="16"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="12"/>
-      <c r="B107" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C107" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="D107" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="E107" s="24"/>
-      <c r="F107" s="19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="12"/>
-      <c r="B108" s="13"/>
-      <c r="C108" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="D108" s="7" t="s">
+      <c r="D121" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F121" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="E108" s="16"/>
-      <c r="F108" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="12"/>
-      <c r="B109" s="21"/>
-      <c r="C109" s="22"/>
-      <c r="D109" s="22"/>
-      <c r="E109" s="23"/>
-      <c r="F109" s="22"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="12"/>
-      <c r="B110" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D110" s="7" t="s">
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="46"/>
+      <c r="B122" s="40"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="46"/>
+      <c r="B123" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="C123" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D123" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E123" s="14"/>
+      <c r="F123" s="14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="46"/>
+      <c r="B124" s="40"/>
+      <c r="C124" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="46"/>
+      <c r="B125" s="40"/>
+      <c r="C125" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="46"/>
+      <c r="B126" s="40"/>
+      <c r="C126" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="46"/>
+      <c r="B127" s="40"/>
+      <c r="C127" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="46"/>
+      <c r="B128" s="40"/>
+      <c r="C128" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="46"/>
+      <c r="B129" s="40"/>
+      <c r="C129" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="46"/>
+      <c r="B130" s="40"/>
+      <c r="C130" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="46"/>
+      <c r="B131" s="40"/>
+      <c r="C131" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="46"/>
+      <c r="B132" s="40"/>
+      <c r="C132" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="46"/>
+      <c r="B133" s="40"/>
+      <c r="C133" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="E110" s="16"/>
-      <c r="F110" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="12"/>
-      <c r="B111" s="13"/>
-      <c r="C111" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="D111" s="7" t="s">
+      <c r="D133" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="E111" s="16"/>
-      <c r="F111" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="31"/>
-      <c r="B112" s="32"/>
-      <c r="C112" s="33"/>
-      <c r="D112" s="33"/>
-      <c r="E112" s="34"/>
-      <c r="F112" s="33"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D113" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="E113" s="10"/>
-      <c r="F113" s="10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="44"/>
-      <c r="B114" s="13"/>
-      <c r="C114" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="44"/>
-      <c r="B115" s="21"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="22"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="22"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="44"/>
-      <c r="B116" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="44"/>
-      <c r="B117" s="13"/>
-      <c r="C117" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="44"/>
-      <c r="B118" s="13"/>
-      <c r="C118" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="44"/>
-      <c r="B119" s="13"/>
-      <c r="C119" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="44"/>
-      <c r="B120" s="13"/>
-      <c r="C120" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="44"/>
-      <c r="B121" s="13"/>
-      <c r="C121" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="44"/>
-      <c r="B122" s="13"/>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="44"/>
-      <c r="B123" s="18" t="s">
+      <c r="F133" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="46"/>
+      <c r="B134" s="40"/>
+      <c r="C134" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="46"/>
+      <c r="B135" s="40"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="46"/>
+      <c r="B136" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="C136" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="E136" s="14"/>
+      <c r="F136" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="C123" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="E123" s="19"/>
-      <c r="F123" s="19" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="44"/>
-      <c r="B124" s="13"/>
-      <c r="C124" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="44"/>
-      <c r="B125" s="13"/>
-      <c r="C125" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D125" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="44"/>
-      <c r="B126" s="13"/>
-      <c r="C126" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="F126" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="44"/>
-      <c r="B127" s="13"/>
-      <c r="C127" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="44"/>
-      <c r="B128" s="13"/>
-      <c r="C128" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="44"/>
-      <c r="B129" s="13"/>
-      <c r="C129" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="44"/>
-      <c r="B130" s="13"/>
-      <c r="C130" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="44"/>
-      <c r="B131" s="13"/>
-      <c r="C131" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="44"/>
-      <c r="B132" s="13"/>
-      <c r="C132" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D132" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="44"/>
-      <c r="B133" s="13"/>
-      <c r="C133" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="44"/>
-      <c r="B134" s="13"/>
-      <c r="C134" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="44"/>
-      <c r="B135" s="13"/>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="44"/>
-      <c r="B136" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="C136" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="D136" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="E136" s="19"/>
-      <c r="F136" s="19" t="s">
-        <v>210</v>
-      </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="44"/>
+      <c r="A137" s="46"/>
       <c r="B137" s="45"/>
       <c r="C137" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="F137" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="D137" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>334</v>
-      </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="44"/>
+      <c r="A138" s="46"/>
       <c r="B138" s="45"/>
       <c r="C138" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="44"/>
+      <c r="A139" s="46"/>
       <c r="B139" s="45"/>
       <c r="C139" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="44"/>
+      <c r="A140" s="46"/>
       <c r="B140" s="45"/>
       <c r="C140" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="44"/>
+      <c r="A141" s="46"/>
       <c r="B141" s="45"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="44"/>
-      <c r="B142" s="18" t="s">
+      <c r="A142" s="46"/>
+      <c r="B142" s="43" t="s">
+        <v>358</v>
+      </c>
+      <c r="C142" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="D142" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="C142" s="19" t="s">
+      <c r="E142" s="14"/>
+      <c r="F142" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="46"/>
+      <c r="B143" s="45"/>
+      <c r="C143" s="31" t="s">
         <v>361</v>
       </c>
-      <c r="D142" s="19" t="s">
+      <c r="D143" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="E142" s="19"/>
-      <c r="F142" s="19" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="44"/>
-      <c r="B143" s="45"/>
-      <c r="C143" s="46" t="s">
-        <v>363</v>
-      </c>
-      <c r="D143" s="46" t="s">
-        <v>364</v>
-      </c>
-      <c r="E143" s="46"/>
-      <c r="F143" s="46" t="s">
-        <v>290</v>
+      <c r="E143" s="31"/>
+      <c r="F143" s="31" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -5010,14 +5018,6 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47290517-900B-4D72-89DA-3AA8C27A191E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D45AEF-0472-4A6A-9988-7C931D1B823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1304,10 +1304,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1439,89 +1439,82 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1893,10 +1886,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -1913,8 +1906,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="40"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="7" t="s">
         <v>84</v>
       </c>
@@ -1929,8 +1922,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
@@ -1938,15 +1931,15 @@
         <v>26</v>
       </c>
       <c r="E4" s="11">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="40"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
@@ -1961,8 +1954,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="40"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
@@ -1977,8 +1970,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
@@ -1993,8 +1986,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="43" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="42" t="s">
         <v>230</v>
       </c>
       <c r="C8" s="14" t="s">
@@ -2011,8 +2004,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="40"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="7" t="s">
         <v>85</v>
       </c>
@@ -2027,8 +2020,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="40"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
@@ -2043,8 +2036,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="40"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
@@ -2059,8 +2052,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="40"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="7" t="s">
         <v>86</v>
       </c>
@@ -2075,8 +2068,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="40"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="7" t="s">
         <v>250</v>
       </c>
@@ -2091,8 +2084,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="40"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="7" t="s">
         <v>13</v>
       </c>
@@ -2107,8 +2100,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="44"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="43"/>
       <c r="C15" s="16" t="s">
         <v>15</v>
       </c>
@@ -2123,8 +2116,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="42" t="s">
         <v>286</v>
       </c>
       <c r="C16" s="14" t="s">
@@ -2141,8 +2134,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="7" t="s">
         <v>84</v>
       </c>
@@ -2157,8 +2150,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="7" t="s">
         <v>10</v>
       </c>
@@ -2173,8 +2166,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="7" t="s">
         <v>11</v>
       </c>
@@ -2189,8 +2182,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>13</v>
       </c>
@@ -2205,8 +2198,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="44"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="43"/>
       <c r="C21" s="16" t="s">
         <v>15</v>
       </c>
@@ -2221,8 +2214,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="36" t="s">
+      <c r="A22" s="32"/>
+      <c r="B22" s="35" t="s">
         <v>229</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -2239,8 +2232,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="36"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="7" t="s">
         <v>296</v>
       </c>
@@ -2255,8 +2248,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33"/>
-      <c r="B24" s="36"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="7" t="s">
         <v>10</v>
       </c>
@@ -2271,8 +2264,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="36"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="7" t="s">
         <v>11</v>
       </c>
@@ -2287,8 +2280,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="33"/>
-      <c r="B26" s="36"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="7" t="s">
         <v>13</v>
       </c>
@@ -2303,8 +2296,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="33"/>
-      <c r="B27" s="36"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="7" t="s">
         <v>15</v>
       </c>
@@ -2319,10 +2312,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="8" t="s">
@@ -2339,8 +2332,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="36"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="7" t="s">
         <v>11</v>
       </c>
@@ -2355,8 +2348,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="36"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="7" t="s">
         <v>13</v>
       </c>
@@ -2371,8 +2364,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="36"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="7" t="s">
         <v>20</v>
       </c>
@@ -2387,8 +2380,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="36"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="7" t="s">
         <v>35</v>
       </c>
@@ -2403,8 +2396,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="36"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="7" t="s">
         <v>36</v>
       </c>
@@ -2419,8 +2412,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="33"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="7" t="s">
         <v>15</v>
       </c>
@@ -2435,8 +2428,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="33"/>
-      <c r="B35" s="37"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="16" t="s">
         <v>88</v>
       </c>
@@ -2451,8 +2444,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="B36" s="38" t="s">
+      <c r="A36" s="32"/>
+      <c r="B36" s="37" t="s">
         <v>333</v>
       </c>
       <c r="C36" s="8" t="s">
@@ -2469,8 +2462,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="36"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="7" t="s">
         <v>11</v>
       </c>
@@ -2485,8 +2478,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="33"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="7" t="s">
         <v>13</v>
       </c>
@@ -2501,8 +2494,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="7" t="s">
         <v>20</v>
       </c>
@@ -2517,8 +2510,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="36"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="7" t="s">
         <v>35</v>
       </c>
@@ -2533,8 +2526,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="B41" s="36"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="7" t="s">
         <v>36</v>
       </c>
@@ -2549,8 +2542,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="36"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="7" t="s">
         <v>15</v>
       </c>
@@ -2565,8 +2558,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="33"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="16" t="s">
         <v>88</v>
       </c>
@@ -2581,8 +2574,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="33"/>
-      <c r="B44" s="38" t="s">
+      <c r="A44" s="32"/>
+      <c r="B44" s="37" t="s">
         <v>201</v>
       </c>
       <c r="C44" s="14" t="s">
@@ -2599,8 +2592,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="B45" s="40"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="39"/>
       <c r="C45" s="7" t="s">
         <v>21</v>
       </c>
@@ -2616,8 +2609,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="33"/>
-      <c r="B46" s="40"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="39"/>
       <c r="C46" s="7" t="s">
         <v>16</v>
       </c>
@@ -2632,8 +2625,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="40"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="39"/>
       <c r="C47" s="7" t="s">
         <v>17</v>
       </c>
@@ -2648,8 +2641,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="33"/>
-      <c r="B48" s="40"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="39"/>
       <c r="C48" s="7" t="s">
         <v>35</v>
       </c>
@@ -2664,8 +2657,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="B49" s="40"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="39"/>
       <c r="C49" s="7" t="s">
         <v>36</v>
       </c>
@@ -2680,8 +2673,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="33"/>
-      <c r="B50" s="40"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="39"/>
       <c r="C50" s="7" t="s">
         <v>89</v>
       </c>
@@ -2696,8 +2689,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="33"/>
-      <c r="B51" s="40"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="39"/>
       <c r="C51" s="7" t="s">
         <v>88</v>
       </c>
@@ -2712,8 +2705,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="40"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="39"/>
       <c r="C52" s="7" t="s">
         <v>13</v>
       </c>
@@ -2728,8 +2721,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="34"/>
-      <c r="B53" s="41"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="40"/>
       <c r="C53" s="21" t="s">
         <v>15</v>
       </c>
@@ -2744,7 +2737,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="32" t="s">
+      <c r="A54" s="31" t="s">
         <v>72</v>
       </c>
       <c r="B54" s="23" t="s">
@@ -2764,8 +2757,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="33"/>
-      <c r="B55" s="38" t="s">
+      <c r="A55" s="32"/>
+      <c r="B55" s="37" t="s">
         <v>4</v>
       </c>
       <c r="C55" s="14" t="s">
@@ -2782,8 +2775,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="33"/>
-      <c r="B56" s="36"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="7" t="s">
         <v>10</v>
       </c>
@@ -2798,8 +2791,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="33"/>
-      <c r="B57" s="36"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="7" t="s">
         <v>17</v>
       </c>
@@ -2814,8 +2807,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="B58" s="36"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="7" t="s">
         <v>18</v>
       </c>
@@ -2830,8 +2823,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="33"/>
-      <c r="B59" s="36"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="7" t="s">
         <v>13</v>
       </c>
@@ -2846,8 +2839,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="33"/>
-      <c r="B60" s="36"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="7" t="s">
         <v>68</v>
       </c>
@@ -2862,8 +2855,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="33"/>
-      <c r="B61" s="37"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="36"/>
       <c r="C61" s="16" t="s">
         <v>15</v>
       </c>
@@ -2878,8 +2871,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="33"/>
-      <c r="B62" s="38" t="s">
+      <c r="A62" s="32"/>
+      <c r="B62" s="37" t="s">
         <v>5</v>
       </c>
       <c r="C62" s="14" t="s">
@@ -2896,8 +2889,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="33"/>
-      <c r="B63" s="36"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="35"/>
       <c r="C63" s="7" t="s">
         <v>10</v>
       </c>
@@ -2912,8 +2905,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33"/>
-      <c r="B64" s="36"/>
+      <c r="A64" s="32"/>
+      <c r="B64" s="35"/>
       <c r="C64" s="7" t="s">
         <v>17</v>
       </c>
@@ -2928,8 +2921,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="36"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="7" t="s">
         <v>18</v>
       </c>
@@ -2944,8 +2937,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
-      <c r="B66" s="36"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="35"/>
       <c r="C66" s="7" t="s">
         <v>13</v>
       </c>
@@ -2960,8 +2953,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
-      <c r="B67" s="36"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="35"/>
       <c r="C67" s="7" t="s">
         <v>68</v>
       </c>
@@ -2976,8 +2969,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="34"/>
-      <c r="B68" s="39"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="38"/>
       <c r="C68" s="21" t="s">
         <v>15</v>
       </c>
@@ -2992,7 +2985,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="32" t="s">
+      <c r="A69" s="31" t="s">
         <v>76</v>
       </c>
       <c r="B69" s="25" t="s">
@@ -3012,7 +3005,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="33"/>
+      <c r="A70" s="32"/>
       <c r="B70" s="6" t="s">
         <v>315</v>
       </c>
@@ -3030,7 +3023,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33"/>
+      <c r="A71" s="32"/>
       <c r="B71" s="28" t="s">
         <v>79</v>
       </c>
@@ -3048,7 +3041,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="34"/>
+      <c r="A72" s="33"/>
       <c r="B72" s="4" t="s">
         <v>274</v>
       </c>
@@ -3122,10 +3115,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
@@ -3140,8 +3133,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="40"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="7" t="s">
         <v>107</v>
       </c>
@@ -3154,8 +3147,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="33"/>
-      <c r="B4" s="40"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="7" t="s">
         <v>84</v>
       </c>
@@ -3168,8 +3161,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="40"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="7" t="s">
         <v>138</v>
       </c>
@@ -3182,8 +3175,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="40"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="7" t="s">
         <v>141</v>
       </c>
@@ -3196,8 +3189,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="40"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="7" t="s">
         <v>155</v>
       </c>
@@ -3210,8 +3203,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="33"/>
-      <c r="B8" s="40"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="39"/>
       <c r="C8" s="7" t="s">
         <v>196</v>
       </c>
@@ -3224,8 +3217,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
-      <c r="B9" s="40"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="7" t="s">
         <v>167</v>
       </c>
@@ -3238,8 +3231,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="33"/>
-      <c r="B10" s="40"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="7" t="s">
         <v>188</v>
       </c>
@@ -3252,13 +3245,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="40"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="39"/>
       <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="43" t="s">
+      <c r="A12" s="32"/>
+      <c r="B12" s="42" t="s">
         <v>230</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -3273,8 +3266,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="33"/>
-      <c r="B13" s="40"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="7" t="s">
         <v>259</v>
       </c>
@@ -3287,8 +3280,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="33"/>
-      <c r="B14" s="40"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="7" t="s">
         <v>139</v>
       </c>
@@ -3301,8 +3294,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="33"/>
-      <c r="B15" s="40"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="39"/>
       <c r="C15" s="7" t="s">
         <v>260</v>
       </c>
@@ -3315,8 +3308,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="40"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
@@ -3329,8 +3322,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="33"/>
-      <c r="B17" s="40"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="7" t="s">
         <v>141</v>
       </c>
@@ -3343,8 +3336,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="33"/>
-      <c r="B18" s="40"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="7" t="s">
         <v>155</v>
       </c>
@@ -3357,8 +3350,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="33"/>
-      <c r="B19" s="40"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="7" t="s">
         <v>196</v>
       </c>
@@ -3371,8 +3364,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="33"/>
-      <c r="B20" s="40"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="7" t="s">
         <v>167</v>
       </c>
@@ -3385,8 +3378,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="40"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="7" t="s">
         <v>188</v>
       </c>
@@ -3399,16 +3392,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="33"/>
-      <c r="B22" s="44"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="43"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
       <c r="E22" s="17"/>
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="33"/>
-      <c r="B23" s="43" t="s">
+      <c r="A23" s="32"/>
+      <c r="B23" s="42" t="s">
         <v>286</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -3423,8 +3416,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33"/>
-      <c r="B24" s="40"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="7" t="s">
         <v>107</v>
       </c>
@@ -3437,8 +3430,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="33"/>
-      <c r="B25" s="40"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="7" t="s">
         <v>84</v>
       </c>
@@ -3451,8 +3444,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="33"/>
-      <c r="B26" s="40"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="7" t="s">
         <v>309</v>
       </c>
@@ -3465,8 +3458,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="33"/>
-      <c r="B27" s="40"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="7" t="s">
         <v>141</v>
       </c>
@@ -3479,8 +3472,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="33"/>
-      <c r="B28" s="40"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="7" t="s">
         <v>155</v>
       </c>
@@ -3493,8 +3486,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="33"/>
-      <c r="B29" s="40"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="7" t="s">
         <v>196</v>
       </c>
@@ -3507,8 +3500,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="33"/>
-      <c r="B30" s="40"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="7" t="s">
         <v>167</v>
       </c>
@@ -3521,8 +3514,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="33"/>
-      <c r="B31" s="40"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="39"/>
       <c r="C31" s="7" t="s">
         <v>188</v>
       </c>
@@ -3535,16 +3528,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="33"/>
-      <c r="B32" s="44"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
       <c r="E32" s="17"/>
       <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="33"/>
-      <c r="B33" s="36" t="s">
+      <c r="A33" s="32"/>
+      <c r="B33" s="35" t="s">
         <v>229</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -3559,8 +3552,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="33"/>
-      <c r="B34" s="36"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="7" t="s">
         <v>107</v>
       </c>
@@ -3573,8 +3566,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="33"/>
-      <c r="B35" s="36"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="7" t="s">
         <v>84</v>
       </c>
@@ -3587,8 +3580,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="33"/>
-      <c r="B36" s="36"/>
+      <c r="A36" s="32"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="7" t="s">
         <v>296</v>
       </c>
@@ -3601,8 +3594,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="33"/>
-      <c r="B37" s="36"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="7" t="s">
         <v>272</v>
       </c>
@@ -3615,8 +3608,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="33"/>
-      <c r="B38" s="36"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="7" t="s">
         <v>141</v>
       </c>
@@ -3629,8 +3622,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="33"/>
-      <c r="B39" s="36"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="7" t="s">
         <v>155</v>
       </c>
@@ -3643,8 +3636,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="33"/>
-      <c r="B40" s="36"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="7" t="s">
         <v>196</v>
       </c>
@@ -3657,8 +3650,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="33"/>
-      <c r="B41" s="36"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="7" t="s">
         <v>167</v>
       </c>
@@ -3671,8 +3664,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="33"/>
-      <c r="B42" s="36"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="7" t="s">
         <v>188</v>
       </c>
@@ -3685,15 +3678,15 @@
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="33"/>
-      <c r="B43" s="36"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="35"/>
       <c r="E43" s="12"/>
     </row>
     <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="34" t="s">
         <v>3</v>
       </c>
       <c r="C44" s="8" t="s">
@@ -3708,8 +3701,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="33"/>
-      <c r="B45" s="36"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="7" t="s">
         <v>111</v>
       </c>
@@ -3722,8 +3715,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="33"/>
-      <c r="B46" s="36"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="7" t="s">
         <v>135</v>
       </c>
@@ -3736,8 +3729,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="33"/>
-      <c r="B47" s="36"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="7" t="s">
         <v>136</v>
       </c>
@@ -3750,8 +3743,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="33"/>
-      <c r="B48" s="36"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="7" t="s">
         <v>141</v>
       </c>
@@ -3764,8 +3757,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="33"/>
-      <c r="B49" s="36"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="7" t="s">
         <v>155</v>
       </c>
@@ -3778,8 +3771,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="33"/>
-      <c r="B50" s="36"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="35"/>
       <c r="C50" s="7" t="s">
         <v>196</v>
       </c>
@@ -3792,8 +3785,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="33"/>
-      <c r="B51" s="36"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="35"/>
       <c r="C51" s="7" t="s">
         <v>167</v>
       </c>
@@ -3806,8 +3799,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="33"/>
-      <c r="B52" s="36"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="35"/>
       <c r="C52" s="7" t="s">
         <v>188</v>
       </c>
@@ -3820,16 +3813,16 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="33"/>
-      <c r="B53" s="37"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="36"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="17"/>
       <c r="F53" s="16"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="33"/>
-      <c r="B54" s="36" t="s">
+      <c r="A54" s="32"/>
+      <c r="B54" s="35" t="s">
         <v>333</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3844,8 +3837,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="33"/>
-      <c r="B55" s="36"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="35"/>
       <c r="C55" s="7" t="s">
         <v>111</v>
       </c>
@@ -3858,8 +3851,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="33"/>
-      <c r="B56" s="36"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="35"/>
       <c r="C56" s="7" t="s">
         <v>135</v>
       </c>
@@ -3872,8 +3865,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="33"/>
-      <c r="B57" s="36"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="35"/>
       <c r="C57" s="7" t="s">
         <v>136</v>
       </c>
@@ -3886,8 +3879,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="33"/>
-      <c r="B58" s="36"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="35"/>
       <c r="C58" s="7" t="s">
         <v>141</v>
       </c>
@@ -3900,8 +3893,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="33"/>
-      <c r="B59" s="36"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="35"/>
       <c r="C59" s="7" t="s">
         <v>155</v>
       </c>
@@ -3914,8 +3907,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="33"/>
-      <c r="B60" s="36"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="35"/>
       <c r="C60" s="7" t="s">
         <v>196</v>
       </c>
@@ -3928,8 +3921,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="33"/>
-      <c r="B61" s="36"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="35"/>
       <c r="C61" s="7" t="s">
         <v>167</v>
       </c>
@@ -3942,8 +3935,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="33"/>
-      <c r="B62" s="36"/>
+      <c r="A62" s="32"/>
+      <c r="B62" s="35"/>
       <c r="C62" s="7" t="s">
         <v>188</v>
       </c>
@@ -3956,13 +3949,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="33"/>
-      <c r="B63" s="37"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="36"/>
       <c r="E63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="33"/>
-      <c r="B64" s="38" t="s">
+      <c r="A64" s="32"/>
+      <c r="B64" s="37" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="14" t="s">
@@ -3977,8 +3970,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="33"/>
-      <c r="B65" s="36"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="35"/>
       <c r="C65" s="7" t="s">
         <v>113</v>
       </c>
@@ -3991,8 +3984,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="33"/>
-      <c r="B66" s="40"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="39"/>
       <c r="C66" s="7" t="s">
         <v>111</v>
       </c>
@@ -4005,8 +3998,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="33"/>
-      <c r="B67" s="40"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="39"/>
       <c r="C67" s="7" t="s">
         <v>107</v>
       </c>
@@ -4019,8 +4012,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="33"/>
-      <c r="B68" s="40"/>
+      <c r="A68" s="32"/>
+      <c r="B68" s="39"/>
       <c r="C68" s="7" t="s">
         <v>126</v>
       </c>
@@ -4033,8 +4026,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="33"/>
-      <c r="B69" s="40"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="39"/>
       <c r="C69" s="7" t="s">
         <v>127</v>
       </c>
@@ -4047,8 +4040,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="33"/>
-      <c r="B70" s="40"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="39"/>
       <c r="C70" s="7" t="s">
         <v>141</v>
       </c>
@@ -4061,8 +4054,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="33"/>
-      <c r="B71" s="40"/>
+      <c r="A71" s="32"/>
+      <c r="B71" s="39"/>
       <c r="C71" s="7" t="s">
         <v>155</v>
       </c>
@@ -4075,8 +4068,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="33"/>
-      <c r="B72" s="40"/>
+      <c r="A72" s="32"/>
+      <c r="B72" s="39"/>
       <c r="C72" s="7" t="s">
         <v>196</v>
       </c>
@@ -4089,8 +4082,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="33"/>
-      <c r="B73" s="40"/>
+      <c r="A73" s="32"/>
+      <c r="B73" s="39"/>
       <c r="C73" s="7" t="s">
         <v>167</v>
       </c>
@@ -4103,8 +4096,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="33"/>
-      <c r="B74" s="40"/>
+      <c r="A74" s="32"/>
+      <c r="B74" s="39"/>
       <c r="C74" s="7" t="s">
         <v>188</v>
       </c>
@@ -4117,18 +4110,18 @@
       </c>
     </row>
     <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="34"/>
-      <c r="B75" s="41"/>
+      <c r="A75" s="33"/>
+      <c r="B75" s="40"/>
       <c r="C75" s="21"/>
       <c r="D75" s="21"/>
       <c r="E75" s="22"/>
       <c r="F75" s="21"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="32" t="s">
+      <c r="A76" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="B76" s="42" t="s">
+      <c r="B76" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
@@ -4143,8 +4136,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="33"/>
-      <c r="B77" s="40"/>
+      <c r="A77" s="32"/>
+      <c r="B77" s="39"/>
       <c r="C77" s="7" t="s">
         <v>153</v>
       </c>
@@ -4157,13 +4150,13 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="33"/>
-      <c r="B78" s="44"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="43"/>
       <c r="E78" s="10"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="33"/>
-      <c r="B79" s="38" t="s">
+      <c r="A79" s="32"/>
+      <c r="B79" s="37" t="s">
         <v>4</v>
       </c>
       <c r="C79" s="14" t="s">
@@ -4178,8 +4171,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="33"/>
-      <c r="B80" s="36"/>
+      <c r="A80" s="32"/>
+      <c r="B80" s="35"/>
       <c r="C80" s="7" t="s">
         <v>107</v>
       </c>
@@ -4192,8 +4185,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="33"/>
-      <c r="B81" s="36"/>
+      <c r="A81" s="32"/>
+      <c r="B81" s="35"/>
       <c r="C81" s="7" t="s">
         <v>122</v>
       </c>
@@ -4206,8 +4199,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="33"/>
-      <c r="B82" s="36"/>
+      <c r="A82" s="32"/>
+      <c r="B82" s="35"/>
       <c r="C82" s="7" t="s">
         <v>141</v>
       </c>
@@ -4220,8 +4213,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="33"/>
-      <c r="B83" s="36"/>
+      <c r="A83" s="32"/>
+      <c r="B83" s="35"/>
       <c r="C83" s="7" t="s">
         <v>155</v>
       </c>
@@ -4234,8 +4227,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="33"/>
-      <c r="B84" s="36"/>
+      <c r="A84" s="32"/>
+      <c r="B84" s="35"/>
       <c r="C84" s="7" t="s">
         <v>161</v>
       </c>
@@ -4248,8 +4241,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="33"/>
-      <c r="B85" s="36"/>
+      <c r="A85" s="32"/>
+      <c r="B85" s="35"/>
       <c r="C85" s="7" t="s">
         <v>196</v>
       </c>
@@ -4262,8 +4255,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="33"/>
-      <c r="B86" s="36"/>
+      <c r="A86" s="32"/>
+      <c r="B86" s="35"/>
       <c r="C86" s="7" t="s">
         <v>167</v>
       </c>
@@ -4276,8 +4269,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="33"/>
-      <c r="B87" s="36"/>
+      <c r="A87" s="32"/>
+      <c r="B87" s="35"/>
       <c r="C87" s="7" t="s">
         <v>188</v>
       </c>
@@ -4290,12 +4283,12 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="33"/>
-      <c r="B88" s="37"/>
+      <c r="A88" s="32"/>
+      <c r="B88" s="36"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="33"/>
-      <c r="B89" s="38" t="s">
+      <c r="A89" s="32"/>
+      <c r="B89" s="37" t="s">
         <v>5</v>
       </c>
       <c r="C89" s="14" t="s">
@@ -4310,8 +4303,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="33"/>
-      <c r="B90" s="36"/>
+      <c r="A90" s="32"/>
+      <c r="B90" s="35"/>
       <c r="C90" s="7" t="s">
         <v>108</v>
       </c>
@@ -4324,8 +4317,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="33"/>
-      <c r="B91" s="36"/>
+      <c r="A91" s="32"/>
+      <c r="B91" s="35"/>
       <c r="C91" s="7" t="s">
         <v>120</v>
       </c>
@@ -4338,8 +4331,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="33"/>
-      <c r="B92" s="36"/>
+      <c r="A92" s="32"/>
+      <c r="B92" s="35"/>
       <c r="C92" s="7" t="s">
         <v>141</v>
       </c>
@@ -4352,8 +4345,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="33"/>
-      <c r="B93" s="36"/>
+      <c r="A93" s="32"/>
+      <c r="B93" s="35"/>
       <c r="C93" s="7" t="s">
         <v>155</v>
       </c>
@@ -4366,8 +4359,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="33"/>
-      <c r="B94" s="36"/>
+      <c r="A94" s="32"/>
+      <c r="B94" s="35"/>
       <c r="C94" s="7" t="s">
         <v>161</v>
       </c>
@@ -4380,8 +4373,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="33"/>
-      <c r="B95" s="36"/>
+      <c r="A95" s="32"/>
+      <c r="B95" s="35"/>
       <c r="C95" s="7" t="s">
         <v>196</v>
       </c>
@@ -4394,8 +4387,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="33"/>
-      <c r="B96" s="36"/>
+      <c r="A96" s="32"/>
+      <c r="B96" s="35"/>
       <c r="C96" s="7" t="s">
         <v>167</v>
       </c>
@@ -4408,8 +4401,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="33"/>
-      <c r="B97" s="36"/>
+      <c r="A97" s="32"/>
+      <c r="B97" s="35"/>
       <c r="C97" s="7" t="s">
         <v>188</v>
       </c>
@@ -4422,14 +4415,14 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="34"/>
-      <c r="B98" s="39"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="38"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="32" t="s">
+      <c r="A99" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="B99" s="42" t="s">
+      <c r="B99" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C99" s="8" t="s">
@@ -4444,8 +4437,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="33"/>
-      <c r="B100" s="40"/>
+      <c r="A100" s="32"/>
+      <c r="B100" s="39"/>
       <c r="C100" s="7" t="s">
         <v>228</v>
       </c>
@@ -4458,8 +4451,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="33"/>
-      <c r="B101" s="40"/>
+      <c r="A101" s="32"/>
+      <c r="B101" s="39"/>
       <c r="C101" s="7" t="s">
         <v>150</v>
       </c>
@@ -4472,16 +4465,16 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="33"/>
-      <c r="B102" s="44"/>
+      <c r="A102" s="32"/>
+      <c r="B102" s="43"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
       <c r="E102" s="17"/>
       <c r="F102" s="16"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="33"/>
-      <c r="B103" s="43" t="s">
+      <c r="A103" s="32"/>
+      <c r="B103" s="42" t="s">
         <v>319</v>
       </c>
       <c r="C103" s="7" t="s">
@@ -4496,8 +4489,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="33"/>
-      <c r="B104" s="40"/>
+      <c r="A104" s="32"/>
+      <c r="B104" s="39"/>
       <c r="C104" s="7" t="s">
         <v>324</v>
       </c>
@@ -4510,8 +4503,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="33"/>
-      <c r="B105" s="40"/>
+      <c r="A105" s="32"/>
+      <c r="B105" s="39"/>
       <c r="C105" s="7" t="s">
         <v>325</v>
       </c>
@@ -4524,13 +4517,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="33"/>
-      <c r="B106" s="44"/>
+      <c r="A106" s="32"/>
+      <c r="B106" s="43"/>
       <c r="E106" s="12"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="33"/>
-      <c r="B107" s="43" t="s">
+      <c r="A107" s="32"/>
+      <c r="B107" s="42" t="s">
         <v>79</v>
       </c>
       <c r="C107" s="14" t="s">
@@ -4545,8 +4538,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="33"/>
-      <c r="B108" s="40"/>
+      <c r="A108" s="32"/>
+      <c r="B108" s="39"/>
       <c r="C108" s="7" t="s">
         <v>151</v>
       </c>
@@ -4559,16 +4552,16 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="33"/>
-      <c r="B109" s="44"/>
+      <c r="A109" s="32"/>
+      <c r="B109" s="43"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
       <c r="E109" s="17"/>
       <c r="F109" s="16"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="33"/>
-      <c r="B110" s="43" t="s">
+      <c r="A110" s="32"/>
+      <c r="B110" s="42" t="s">
         <v>274</v>
       </c>
       <c r="C110" s="7" t="s">
@@ -4583,8 +4576,8 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="33"/>
-      <c r="B111" s="40"/>
+      <c r="A111" s="32"/>
+      <c r="B111" s="39"/>
       <c r="C111" s="7" t="s">
         <v>275</v>
       </c>
@@ -4597,18 +4590,18 @@
       </c>
     </row>
     <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="34"/>
-      <c r="B112" s="41"/>
+      <c r="A112" s="33"/>
+      <c r="B112" s="40"/>
       <c r="C112" s="21"/>
       <c r="D112" s="21"/>
       <c r="E112" s="22"/>
       <c r="F112" s="21"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="32" t="s">
+      <c r="A113" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B113" s="42" t="s">
+      <c r="B113" s="41" t="s">
         <v>13</v>
       </c>
       <c r="C113" s="8" t="s">
@@ -4623,8 +4616,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="46"/>
-      <c r="B114" s="40"/>
+      <c r="A114" s="32"/>
+      <c r="B114" s="39"/>
       <c r="C114" s="7" t="s">
         <v>174</v>
       </c>
@@ -4636,16 +4629,16 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="46"/>
-      <c r="B115" s="44"/>
+      <c r="A115" s="32"/>
+      <c r="B115" s="43"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="46"/>
-      <c r="B116" s="43" t="s">
+      <c r="A116" s="32"/>
+      <c r="B116" s="42" t="s">
         <v>183</v>
       </c>
       <c r="C116" s="7" t="s">
@@ -4659,8 +4652,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="46"/>
-      <c r="B117" s="40"/>
+      <c r="A117" s="32"/>
+      <c r="B117" s="39"/>
       <c r="C117" s="7" t="s">
         <v>181</v>
       </c>
@@ -4672,8 +4665,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="46"/>
-      <c r="B118" s="40"/>
+      <c r="A118" s="32"/>
+      <c r="B118" s="39"/>
       <c r="C118" s="7" t="s">
         <v>177</v>
       </c>
@@ -4685,8 +4678,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="46"/>
-      <c r="B119" s="40"/>
+      <c r="A119" s="32"/>
+      <c r="B119" s="39"/>
       <c r="C119" s="7" t="s">
         <v>179</v>
       </c>
@@ -4698,8 +4691,8 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="46"/>
-      <c r="B120" s="40"/>
+      <c r="A120" s="32"/>
+      <c r="B120" s="39"/>
       <c r="C120" s="7" t="s">
         <v>182</v>
       </c>
@@ -4711,8 +4704,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="46"/>
-      <c r="B121" s="40"/>
+      <c r="A121" s="32"/>
+      <c r="B121" s="39"/>
       <c r="C121" s="7" t="s">
         <v>191</v>
       </c>
@@ -4724,12 +4717,12 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="46"/>
-      <c r="B122" s="40"/>
+      <c r="A122" s="32"/>
+      <c r="B122" s="39"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="46"/>
-      <c r="B123" s="43" t="s">
+      <c r="A123" s="32"/>
+      <c r="B123" s="42" t="s">
         <v>206</v>
       </c>
       <c r="C123" s="14" t="s">
@@ -4744,8 +4737,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="46"/>
-      <c r="B124" s="40"/>
+      <c r="A124" s="32"/>
+      <c r="B124" s="39"/>
       <c r="C124" s="7" t="s">
         <v>204</v>
       </c>
@@ -4757,8 +4750,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="46"/>
-      <c r="B125" s="40"/>
+      <c r="A125" s="32"/>
+      <c r="B125" s="39"/>
       <c r="C125" s="7" t="s">
         <v>215</v>
       </c>
@@ -4770,8 +4763,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="46"/>
-      <c r="B126" s="40"/>
+      <c r="A126" s="32"/>
+      <c r="B126" s="39"/>
       <c r="C126" s="7" t="s">
         <v>205</v>
       </c>
@@ -4783,8 +4776,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="46"/>
-      <c r="B127" s="40"/>
+      <c r="A127" s="32"/>
+      <c r="B127" s="39"/>
       <c r="C127" s="7" t="s">
         <v>328</v>
       </c>
@@ -4796,8 +4789,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="46"/>
-      <c r="B128" s="40"/>
+      <c r="A128" s="32"/>
+      <c r="B128" s="39"/>
       <c r="C128" s="7" t="s">
         <v>352</v>
       </c>
@@ -4809,8 +4802,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="46"/>
-      <c r="B129" s="40"/>
+      <c r="A129" s="32"/>
+      <c r="B129" s="39"/>
       <c r="C129" s="7" t="s">
         <v>354</v>
       </c>
@@ -4822,8 +4815,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="46"/>
-      <c r="B130" s="40"/>
+      <c r="A130" s="32"/>
+      <c r="B130" s="39"/>
       <c r="C130" s="7" t="s">
         <v>217</v>
       </c>
@@ -4835,8 +4828,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="46"/>
-      <c r="B131" s="40"/>
+      <c r="A131" s="32"/>
+      <c r="B131" s="39"/>
       <c r="C131" s="7" t="s">
         <v>221</v>
       </c>
@@ -4848,8 +4841,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="46"/>
-      <c r="B132" s="40"/>
+      <c r="A132" s="32"/>
+      <c r="B132" s="39"/>
       <c r="C132" s="7" t="s">
         <v>202</v>
       </c>
@@ -4861,8 +4854,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="46"/>
-      <c r="B133" s="40"/>
+      <c r="A133" s="32"/>
+      <c r="B133" s="39"/>
       <c r="C133" s="7" t="s">
         <v>278</v>
       </c>
@@ -4874,8 +4867,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="46"/>
-      <c r="B134" s="40"/>
+      <c r="A134" s="32"/>
+      <c r="B134" s="39"/>
       <c r="C134" s="7" t="s">
         <v>281</v>
       </c>
@@ -4887,12 +4880,12 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="46"/>
-      <c r="B135" s="40"/>
+      <c r="A135" s="32"/>
+      <c r="B135" s="39"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="46"/>
-      <c r="B136" s="43" t="s">
+      <c r="A136" s="32"/>
+      <c r="B136" s="42" t="s">
         <v>222</v>
       </c>
       <c r="C136" s="14" t="s">
@@ -4907,8 +4900,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="46"/>
-      <c r="B137" s="45"/>
+      <c r="A137" s="32"/>
+      <c r="B137" s="39"/>
       <c r="C137" s="7" t="s">
         <v>330</v>
       </c>
@@ -4920,8 +4913,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="46"/>
-      <c r="B138" s="45"/>
+      <c r="A138" s="32"/>
+      <c r="B138" s="39"/>
       <c r="C138" s="7" t="s">
         <v>225</v>
       </c>
@@ -4933,8 +4926,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="46"/>
-      <c r="B139" s="45"/>
+      <c r="A139" s="32"/>
+      <c r="B139" s="39"/>
       <c r="C139" s="7" t="s">
         <v>282</v>
       </c>
@@ -4946,8 +4939,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="46"/>
-      <c r="B140" s="45"/>
+      <c r="A140" s="32"/>
+      <c r="B140" s="39"/>
       <c r="C140" s="7" t="s">
         <v>284</v>
       </c>
@@ -4959,12 +4952,12 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="46"/>
-      <c r="B141" s="45"/>
+      <c r="A141" s="32"/>
+      <c r="B141" s="39"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="46"/>
-      <c r="B142" s="43" t="s">
+      <c r="A142" s="32"/>
+      <c r="B142" s="42" t="s">
         <v>358</v>
       </c>
       <c r="C142" s="14" t="s">
@@ -4979,29 +4972,20 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="46"/>
-      <c r="B143" s="45"/>
-      <c r="C143" s="31" t="s">
+      <c r="A143" s="32"/>
+      <c r="B143" s="39"/>
+      <c r="C143" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="D143" s="31" t="s">
+      <c r="D143" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="E143" s="31"/>
-      <c r="F143" s="31" t="s">
+      <c r="F143" s="7" t="s">
         <v>288</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="A113:A143"/>
     <mergeCell ref="A2:A43"/>
@@ -5018,6 +5002,14 @@
     <mergeCell ref="B116:B122"/>
     <mergeCell ref="B123:B135"/>
     <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B99:B102"/>
+    <mergeCell ref="B103:B106"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Greenfield_Südafrika/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Südafrika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Greenfield_Südafrika\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D45AEF-0472-4A6A-9988-7C931D1B823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D123030-36D3-4CB6-96BA-4A1F63E42441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-53868" yWindow="3444" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="362">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -882,12 +882,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>CO2-Bereitstellung / Direct Air Capture</t>
   </si>
   <si>
@@ -1167,13 +1161,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1304,10 +1292,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1439,44 +1427,44 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1988,19 +1976,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="32"/>
       <c r="B8" s="42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E8" s="15">
         <v>1.5</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2010,7 +1998,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E9" s="10">
         <v>285.39999999999998</v>
@@ -2026,13 +2014,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E10" s="10">
         <v>5110</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2042,7 +2030,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E11" s="12">
         <v>0.05</v>
@@ -2058,29 +2046,29 @@
         <v>86</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E12" s="10">
         <v>0.189</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="32"/>
       <c r="B13" s="39"/>
       <c r="C13" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E13" s="10">
         <v>1.375</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2090,7 +2078,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E14" s="13">
         <v>25</v>
@@ -2106,7 +2094,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E15" s="17">
         <v>0.08</v>
@@ -2118,13 +2106,13 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="32"/>
       <c r="B16" s="42" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E16" s="18">
         <v>3.7</v>
@@ -2140,13 +2128,13 @@
         <v>84</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E17" s="12">
         <v>0.27</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2156,13 +2144,13 @@
         <v>10</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E18" s="12">
         <v>700</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2172,7 +2160,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E19" s="12">
         <v>0.02</v>
@@ -2188,7 +2176,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E20" s="12">
         <v>20</v>
@@ -2204,7 +2192,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E21" s="17">
         <v>0.05</v>
@@ -2216,35 +2204,35 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="32"/>
       <c r="B22" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E22" s="10">
         <v>0.5</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="32"/>
       <c r="B23" s="35"/>
       <c r="C23" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E23" s="10">
         <v>1.75</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2254,13 +2242,13 @@
         <v>10</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E24" s="10">
         <v>7000</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2270,7 +2258,7 @@
         <v>11</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E25" s="12">
         <v>0.05</v>
@@ -2286,7 +2274,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E26" s="13">
         <v>15</v>
@@ -2302,7 +2290,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E27" s="12">
         <v>7.0000000000000007E-2</v>
@@ -2446,19 +2434,19 @@
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="32"/>
       <c r="B36" s="37" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>87</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E36" s="19">
         <v>2.83</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2468,7 +2456,7 @@
         <v>11</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E37" s="12">
         <v>0.03</v>
@@ -2484,7 +2472,7 @@
         <v>13</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E38" s="13">
         <v>30</v>
@@ -2500,7 +2488,7 @@
         <v>20</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E39" s="12">
         <v>7.3999999999999999E-4</v>
@@ -2516,7 +2504,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E40" s="12">
         <v>0.98</v>
@@ -2532,7 +2520,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E41" s="12">
         <v>0.98</v>
@@ -2548,7 +2536,7 @@
         <v>15</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E42" s="12">
         <v>0.05</v>
@@ -2564,7 +2552,7 @@
         <v>88</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E43" s="17">
         <v>0</v>
@@ -2998,7 +2986,7 @@
         <v>78</v>
       </c>
       <c r="E69" s="27">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="26" t="s">
         <v>19</v>
@@ -3007,19 +2995,19 @@
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="32"/>
       <c r="B70" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="D70" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>317</v>
-      </c>
       <c r="E70" s="12">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -3043,19 +3031,19 @@
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="33"/>
       <c r="B72" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E72" s="22">
         <v>-0.6</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -3082,7 +3070,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="7" customWidth="1"/>
@@ -3252,13 +3240,13 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="32"/>
       <c r="B12" s="42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="14" t="s">
@@ -3269,14 +3257,14 @@
       <c r="A13" s="32"/>
       <c r="B13" s="39"/>
       <c r="C13" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3286,7 +3274,7 @@
         <v>139</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10" t="s">
@@ -3297,14 +3285,14 @@
       <c r="A15" s="32"/>
       <c r="B15" s="39"/>
       <c r="C15" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3314,7 +3302,7 @@
         <v>84</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="7" t="s">
@@ -3328,7 +3316,7 @@
         <v>141</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E17" s="10"/>
       <c r="F17" s="7" t="s">
@@ -3342,7 +3330,7 @@
         <v>155</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E18" s="13"/>
       <c r="F18" s="7" t="s">
@@ -3356,7 +3344,7 @@
         <v>196</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="7" t="s">
@@ -3370,7 +3358,7 @@
         <v>167</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E20" s="13"/>
       <c r="F20" s="7" t="s">
@@ -3384,7 +3372,7 @@
         <v>188</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="7" t="s">
@@ -3402,17 +3390,17 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="32"/>
       <c r="B23" s="42" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -3422,7 +3410,7 @@
         <v>107</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="7" t="s">
@@ -3436,25 +3424,25 @@
         <v>84</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="32"/>
       <c r="B26" s="39"/>
       <c r="C26" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E26" s="13"/>
       <c r="F26" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3464,7 +3452,7 @@
         <v>141</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="7" t="s">
@@ -3478,7 +3466,7 @@
         <v>155</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E28" s="13"/>
       <c r="F28" s="7" t="s">
@@ -3492,7 +3480,7 @@
         <v>196</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E29" s="13"/>
       <c r="F29" s="7" t="s">
@@ -3506,7 +3494,7 @@
         <v>167</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E30" s="12"/>
       <c r="F30" s="7" t="s">
@@ -3520,7 +3508,7 @@
         <v>188</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E31" s="12"/>
       <c r="F31" s="7" t="s">
@@ -3538,13 +3526,13 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="32"/>
       <c r="B33" s="35" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>96</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E33" s="10"/>
       <c r="F33" s="7" t="s">
@@ -3558,7 +3546,7 @@
         <v>107</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E34" s="10"/>
       <c r="F34" s="7" t="s">
@@ -3572,7 +3560,7 @@
         <v>84</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="7" t="s">
@@ -3583,28 +3571,28 @@
       <c r="A36" s="32"/>
       <c r="B36" s="35"/>
       <c r="C36" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E36" s="12"/>
       <c r="F36" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="32"/>
       <c r="B37" s="35"/>
       <c r="C37" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E37" s="13"/>
       <c r="F37" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -3614,7 +3602,7 @@
         <v>141</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E38" s="13"/>
       <c r="F38" s="7" t="s">
@@ -3628,7 +3616,7 @@
         <v>155</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="7" t="s">
@@ -3642,7 +3630,7 @@
         <v>196</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E40" s="13"/>
       <c r="F40" s="7" t="s">
@@ -3656,7 +3644,7 @@
         <v>167</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="7" t="s">
@@ -3670,7 +3658,7 @@
         <v>188</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="7" t="s">
@@ -3697,7 +3685,7 @@
       </c>
       <c r="E44" s="19"/>
       <c r="F44" s="8" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -3711,7 +3699,7 @@
       </c>
       <c r="E45" s="12"/>
       <c r="F45" s="7" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -3823,17 +3811,17 @@
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="32"/>
       <c r="B54" s="35" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>113</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E54" s="10"/>
       <c r="F54" s="7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -3843,11 +3831,11 @@
         <v>111</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E55" s="12"/>
       <c r="F55" s="7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -3857,11 +3845,11 @@
         <v>135</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E56" s="13"/>
       <c r="F56" s="7" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -3871,11 +3859,11 @@
         <v>136</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E57" s="12"/>
       <c r="F57" s="7" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -3885,7 +3873,7 @@
         <v>141</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="7" t="s">
@@ -3899,7 +3887,7 @@
         <v>155</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E59" s="12"/>
       <c r="F59" s="7" t="s">
@@ -3913,7 +3901,7 @@
         <v>196</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E60" s="12"/>
       <c r="F60" s="7" t="s">
@@ -3927,7 +3915,7 @@
         <v>167</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E61" s="12"/>
       <c r="F61" s="7" t="s">
@@ -3941,7 +3929,7 @@
         <v>188</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E62" s="12"/>
       <c r="F62" s="7" t="s">
@@ -4440,10 +4428,10 @@
       <c r="A100" s="32"/>
       <c r="B100" s="39"/>
       <c r="C100" s="7" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E100" s="12"/>
       <c r="F100" s="7" t="s">
@@ -4452,200 +4440,198 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="32"/>
-      <c r="B101" s="39"/>
-      <c r="C101" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E101" s="12"/>
-      <c r="F101" s="7" t="s">
-        <v>149</v>
-      </c>
+      <c r="B101" s="43"/>
+      <c r="C101" s="16"/>
+      <c r="D101" s="16"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="16"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="32"/>
-      <c r="B102" s="43"/>
-      <c r="C102" s="16"/>
-      <c r="D102" s="16"/>
-      <c r="E102" s="17"/>
-      <c r="F102" s="16"/>
+      <c r="B102" s="42" t="s">
+        <v>317</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E102" s="12"/>
+      <c r="F102" s="7" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="32"/>
-      <c r="B103" s="42" t="s">
-        <v>319</v>
-      </c>
+      <c r="B103" s="39"/>
       <c r="C103" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="D103" s="7" t="s">
         <v>320</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>321</v>
       </c>
       <c r="E103" s="12"/>
       <c r="F103" s="7" t="s">
-        <v>308</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="32"/>
-      <c r="B104" s="39"/>
-      <c r="C104" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>322</v>
-      </c>
+      <c r="B104" s="43"/>
       <c r="E104" s="12"/>
-      <c r="F104" s="7" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="32"/>
-      <c r="B105" s="39"/>
-      <c r="C105" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="E105" s="12"/>
-      <c r="F105" s="7" t="s">
-        <v>149</v>
+      <c r="B105" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D105" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E105" s="18"/>
+      <c r="F105" s="14" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="32"/>
-      <c r="B106" s="43"/>
+      <c r="B106" s="39"/>
+      <c r="C106" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>148</v>
+      </c>
       <c r="E106" s="12"/>
+      <c r="F106" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="32"/>
-      <c r="B107" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="C107" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D107" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="E107" s="18"/>
-      <c r="F107" s="14" t="s">
-        <v>132</v>
-      </c>
+      <c r="B107" s="43"/>
+      <c r="C107" s="16"/>
+      <c r="D107" s="16"/>
+      <c r="E107" s="17"/>
+      <c r="F107" s="16"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="32"/>
-      <c r="B108" s="39"/>
+      <c r="B108" s="42" t="s">
+        <v>272</v>
+      </c>
       <c r="C108" s="7" t="s">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="D108" s="7" t="s">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="E108" s="12"/>
       <c r="F108" s="7" t="s">
-        <v>149</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="32"/>
-      <c r="B109" s="43"/>
-      <c r="C109" s="16"/>
-      <c r="D109" s="16"/>
-      <c r="E109" s="17"/>
-      <c r="F109" s="16"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="32"/>
-      <c r="B110" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="C110" s="7" t="s">
+      <c r="B109" s="39"/>
+      <c r="C109" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="D110" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E110" s="12"/>
-      <c r="F110" s="7" t="s">
-        <v>262</v>
-      </c>
+      <c r="D109" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E109" s="12"/>
+      <c r="F109" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="33"/>
+      <c r="B110" s="40"/>
+      <c r="C110" s="21"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="21"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="32"/>
-      <c r="B111" s="39"/>
-      <c r="C111" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="E111" s="12"/>
-      <c r="F111" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="33"/>
-      <c r="B112" s="40"/>
-      <c r="C112" s="21"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="22"/>
-      <c r="F112" s="21"/>
+      <c r="A111" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="B111" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="32"/>
+      <c r="B112" s="39"/>
+      <c r="C112" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="B113" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="D113" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="E113" s="8"/>
-      <c r="F113" s="8" t="s">
-        <v>140</v>
-      </c>
+      <c r="A113" s="32"/>
+      <c r="B113" s="43"/>
+      <c r="C113" s="16"/>
+      <c r="D113" s="16"/>
+      <c r="E113" s="16"/>
+      <c r="F113" s="16"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="32"/>
-      <c r="B114" s="39"/>
+      <c r="B114" s="42" t="s">
+        <v>183</v>
+      </c>
       <c r="C114" s="7" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="32"/>
-      <c r="B115" s="43"/>
-      <c r="C115" s="16"/>
-      <c r="D115" s="16"/>
-      <c r="E115" s="16"/>
-      <c r="F115" s="16"/>
+      <c r="B115" s="39"/>
+      <c r="C115" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="32"/>
-      <c r="B116" s="42" t="s">
-        <v>183</v>
-      </c>
+      <c r="B116" s="39"/>
       <c r="C116" s="7" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D116" s="7" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>149</v>
@@ -4655,10 +4641,10 @@
       <c r="A117" s="32"/>
       <c r="B117" s="39"/>
       <c r="C117" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D117" s="7" t="s">
-        <v>327</v>
+        <v>178</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>149</v>
@@ -4668,10 +4654,10 @@
       <c r="A118" s="32"/>
       <c r="B118" s="39"/>
       <c r="C118" s="7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>149</v>
@@ -4681,10 +4667,10 @@
       <c r="A119" s="32"/>
       <c r="B119" s="39"/>
       <c r="C119" s="7" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>149</v>
@@ -4693,57 +4679,57 @@
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="32"/>
       <c r="B120" s="39"/>
-      <c r="C120" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="32"/>
-      <c r="B121" s="39"/>
-      <c r="C121" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>149</v>
+      <c r="B121" s="42" t="s">
+        <v>206</v>
+      </c>
+      <c r="C121" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D121" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="E121" s="14"/>
+      <c r="F121" s="14" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="32"/>
       <c r="B122" s="39"/>
+      <c r="C122" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="32"/>
-      <c r="B123" s="42" t="s">
-        <v>206</v>
-      </c>
-      <c r="C123" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D123" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="E123" s="14"/>
-      <c r="F123" s="14" t="s">
-        <v>208</v>
+      <c r="B123" s="39"/>
+      <c r="C123" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="32"/>
       <c r="B124" s="39"/>
       <c r="C124" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>208</v>
@@ -4753,88 +4739,88 @@
       <c r="A125" s="32"/>
       <c r="B125" s="39"/>
       <c r="C125" s="7" t="s">
-        <v>215</v>
+        <v>324</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>214</v>
+        <v>325</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>219</v>
+        <v>328</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="32"/>
       <c r="B126" s="39"/>
       <c r="C126" s="7" t="s">
-        <v>205</v>
+        <v>348</v>
       </c>
       <c r="D126" s="7" t="s">
-        <v>209</v>
+        <v>349</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>208</v>
+        <v>328</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="32"/>
       <c r="B127" s="39"/>
       <c r="C127" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="F127" s="7" t="s">
         <v>328</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="32"/>
       <c r="B128" s="39"/>
       <c r="C128" s="7" t="s">
-        <v>352</v>
+        <v>217</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>353</v>
+        <v>216</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>332</v>
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="32"/>
       <c r="B129" s="39"/>
       <c r="C129" s="7" t="s">
-        <v>354</v>
+        <v>221</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>355</v>
+        <v>211</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>332</v>
+        <v>212</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="32"/>
       <c r="B130" s="39"/>
       <c r="C130" s="7" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D130" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="32"/>
       <c r="B131" s="39"/>
       <c r="C131" s="7" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="D131" s="7" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="F131" s="7" t="s">
         <v>212</v>
@@ -4844,150 +4830,124 @@
       <c r="A132" s="32"/>
       <c r="B132" s="39"/>
       <c r="C132" s="7" t="s">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="32"/>
       <c r="B133" s="39"/>
-      <c r="C133" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>212</v>
-      </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="32"/>
-      <c r="B134" s="39"/>
-      <c r="C134" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>213</v>
+      <c r="B134" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="C134" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="D134" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="E134" s="14"/>
+      <c r="F134" s="14" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="32"/>
       <c r="B135" s="39"/>
+      <c r="C135" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="32"/>
-      <c r="B136" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="C136" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="D136" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="E136" s="14"/>
-      <c r="F136" s="14" t="s">
-        <v>208</v>
+      <c r="B136" s="39"/>
+      <c r="C136" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="32"/>
       <c r="B137" s="39"/>
       <c r="C137" s="7" t="s">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>331</v>
+        <v>281</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>332</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="32"/>
       <c r="B138" s="39"/>
       <c r="C138" s="7" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>226</v>
+        <v>322</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="32"/>
       <c r="B139" s="39"/>
-      <c r="C139" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>212</v>
-      </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="32"/>
-      <c r="B140" s="39"/>
-      <c r="C140" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D140" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>213</v>
+      <c r="B140" s="42" t="s">
+        <v>354</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="D140" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="E140" s="14"/>
+      <c r="F140" s="14" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="32"/>
       <c r="B141" s="39"/>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="32"/>
-      <c r="B142" s="42" t="s">
+      <c r="C141" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D141" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="C142" s="14" t="s">
-        <v>359</v>
-      </c>
-      <c r="D142" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="E142" s="14"/>
-      <c r="F142" s="14" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="32"/>
-      <c r="B143" s="39"/>
-      <c r="C143" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>288</v>
+      <c r="F141" s="7" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="A113:A143"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="A111:A141"/>
     <mergeCell ref="A2:A43"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -4997,19 +4957,19 @@
     <mergeCell ref="B23:B32"/>
     <mergeCell ref="B44:B53"/>
     <mergeCell ref="B54:B63"/>
-    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="B108:B110"/>
     <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B116:B122"/>
-    <mergeCell ref="B123:B135"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B136:B141"/>
+    <mergeCell ref="B114:B120"/>
+    <mergeCell ref="B121:B133"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B134:B139"/>
     <mergeCell ref="A76:A98"/>
     <mergeCell ref="B79:B88"/>
     <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
+    <mergeCell ref="A99:A110"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="B99:B101"/>
+    <mergeCell ref="B102:B104"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
